--- a/نموذج_طلبية_ورشة.xlsx
+++ b/نموذج_طلبية_ورشة.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'طلبية'!$11:$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'طلبية'!$A$1:$I$51</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,6 +193,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -738,9 +741,27 @@
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="5" t="n"/>
     </row>
-    <row r="5"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>الورقة رقم</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>من أصل</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>الطلبية الطويلة تنقسم ورقتين — وكل ورقة بتحمل عدد بنودها هي، لا عدد الطلبية كلها</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>◆ ضوابط التدقيق — تُملأ من الورقة الأصلية قبل البدء بالإدخال ◆</t>
         </is>
@@ -758,12 +779,12 @@
           <t>المُدخَل فعلياً</t>
         </is>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>COUNTA(B12:B46)</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IF(B7="","— اكتب عدد بنود الورقة أولاً",IF(D7=B7,"✅ مطابق — ما في بند ناقص",IF(D7&lt;B7,"⛔ ناقص "&amp;(B7-D7)&amp;" بند — راجع الورقة","⛔ زائد "&amp;(D7-B7)&amp;" بند — في بند مكرر")))</f>
+      <c r="E7" s="8">
+        <f>IF(B7="","— اكتب عدد بنود هاي الورقة أولاً",IF(D7=B7,"✅ مطابق — ما في بند ناقص",IF(D7&lt;B7,"⛔ ناقص "&amp;(B7-D7)&amp;" بند — راجع الورقة","⛔ زائد "&amp;(D7-B7)&amp;" بند — في بند مكرر")))</f>
         <v/>
       </c>
     </row>
@@ -779,11 +800,11 @@
           <t>المُدخَل فعلياً</t>
         </is>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>SUM(C12:C46)</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>IF(B8="","— اختياري (موصى به للطلبيات فوق 10 بنود)",IF(ROUND(D8,3)=ROUND(B8,3),"✅ مطابق","⛔ فرق "&amp;TEXT(D8-B8,"0.###")&amp;" — في كمية مكتوبة غلط"))</f>
         <v/>
       </c>
@@ -794,7 +815,7 @@
           <t>البنود المدقَّقة ✔</t>
         </is>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <f>COUNTIF(H12:H46,"✔")</f>
         <v/>
       </c>
@@ -803,679 +824,679 @@
           <t>الحالة النهائية</t>
         </is>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="9">
         <f>IF(D7=0,"⛔ ما في بنود مُدخلة",IF(B7="","⛔ ناقص: عدد البنود حسب الأصل",IF(D7&lt;&gt;B7,"⛔ عدد البنود مش مطابق",IF(B9&lt;D7,"⛔ باقي "&amp;(D7-B9)&amp;" بند بدون تدقيق","✅ جاهز للترحيل — ابعثها للأستاذ"))))</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>البند (كما طلع من المحل)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>الكمية</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>الوحدة</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>السعر الإفرادي</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>المجموع</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>تاريخ الإخراج</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>✔ تدقيق</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>ملاحظات</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <f>IF(B12="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="15">
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="16">
         <f>IF(OR(C12="",E12=""),"",C12*E12)</f>
         <v/>
       </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="11" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="12" t="n"/>
     </row>
     <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <f>IF(B13="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="13" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="15">
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="16">
         <f>IF(OR(C13="",E13=""),"",C13*E13)</f>
         <v/>
       </c>
-      <c r="G13" s="16" t="n"/>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="11" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="12" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <f>IF(B14="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="15">
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="16">
         <f>IF(OR(C14="",E14=""),"",C14*E14)</f>
         <v/>
       </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="11" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="12" t="n"/>
     </row>
     <row r="15" ht="19" customHeight="1">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <f>IF(B15="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="13" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="15">
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="16">
         <f>IF(OR(C15="",E15=""),"",C15*E15)</f>
         <v/>
       </c>
-      <c r="G15" s="16" t="n"/>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="11" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="12" t="n"/>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <f>IF(B16="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="15">
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="16">
         <f>IF(OR(C16="",E16=""),"",C16*E16)</f>
         <v/>
       </c>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="11" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="12" t="n"/>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <f>IF(B17="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="15">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="14" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="16">
         <f>IF(OR(C17="",E17=""),"",C17*E17)</f>
         <v/>
       </c>
-      <c r="G17" s="16" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="11" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="12" t="n"/>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <f>IF(B18="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="15">
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="16">
         <f>IF(OR(C18="",E18=""),"",C18*E18)</f>
         <v/>
       </c>
-      <c r="G18" s="16" t="n"/>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="11" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="12" t="n"/>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="10">
+      <c r="A19" s="11">
         <f>IF(B19="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="15">
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="16">
         <f>IF(OR(C19="",E19=""),"",C19*E19)</f>
         <v/>
       </c>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="11" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="12" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="10">
+      <c r="A20" s="11">
         <f>IF(B20="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="15">
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="16">
         <f>IF(OR(C20="",E20=""),"",C20*E20)</f>
         <v/>
       </c>
-      <c r="G20" s="16" t="n"/>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="11" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="12" t="n"/>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <f>IF(B21="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="15">
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="16">
         <f>IF(OR(C21="",E21=""),"",C21*E21)</f>
         <v/>
       </c>
-      <c r="G21" s="16" t="n"/>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="11" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="12" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="10">
+      <c r="A22" s="11">
         <f>IF(B22="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="15">
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="16">
         <f>IF(OR(C22="",E22=""),"",C22*E22)</f>
         <v/>
       </c>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="11" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="12" t="n"/>
     </row>
     <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="10">
+      <c r="A23" s="11">
         <f>IF(B23="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="15">
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="16">
         <f>IF(OR(C23="",E23=""),"",C23*E23)</f>
         <v/>
       </c>
-      <c r="G23" s="16" t="n"/>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="11" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="12" t="n"/>
     </row>
     <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="10">
+      <c r="A24" s="11">
         <f>IF(B24="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="15">
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="16">
         <f>IF(OR(C24="",E24=""),"",C24*E24)</f>
         <v/>
       </c>
-      <c r="G24" s="16" t="n"/>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="11" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="12" t="n"/>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="10">
+      <c r="A25" s="11">
         <f>IF(B25="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="15">
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="16">
         <f>IF(OR(C25="",E25=""),"",C25*E25)</f>
         <v/>
       </c>
-      <c r="G25" s="16" t="n"/>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="11" t="n"/>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="12" t="n"/>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="A26" s="10">
+      <c r="A26" s="11">
         <f>IF(B26="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="15">
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="16">
         <f>IF(OR(C26="",E26=""),"",C26*E26)</f>
         <v/>
       </c>
-      <c r="G26" s="16" t="n"/>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="11" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="14" t="n"/>
+      <c r="I26" s="12" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="10">
+      <c r="A27" s="11">
         <f>IF(B27="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="14" t="n"/>
-      <c r="F27" s="15">
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="16">
         <f>IF(OR(C27="",E27=""),"",C27*E27)</f>
         <v/>
       </c>
-      <c r="G27" s="16" t="n"/>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="11" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="14" t="n"/>
+      <c r="I27" s="12" t="n"/>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="10">
+      <c r="A28" s="11">
         <f>IF(B28="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="14" t="n"/>
-      <c r="F28" s="15">
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="16">
         <f>IF(OR(C28="",E28=""),"",C28*E28)</f>
         <v/>
       </c>
-      <c r="G28" s="16" t="n"/>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="11" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="12" t="n"/>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="10">
+      <c r="A29" s="11">
         <f>IF(B29="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="14" t="n"/>
-      <c r="F29" s="15">
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="16">
         <f>IF(OR(C29="",E29=""),"",C29*E29)</f>
         <v/>
       </c>
-      <c r="G29" s="16" t="n"/>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="11" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="14" t="n"/>
+      <c r="I29" s="12" t="n"/>
     </row>
     <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="10">
+      <c r="A30" s="11">
         <f>IF(B30="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="15">
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="16">
         <f>IF(OR(C30="",E30=""),"",C30*E30)</f>
         <v/>
       </c>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="11" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="14" t="n"/>
+      <c r="I30" s="12" t="n"/>
     </row>
     <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="10">
+      <c r="A31" s="11">
         <f>IF(B31="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="15">
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="16">
         <f>IF(OR(C31="",E31=""),"",C31*E31)</f>
         <v/>
       </c>
-      <c r="G31" s="16" t="n"/>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="11" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="14" t="n"/>
+      <c r="I31" s="12" t="n"/>
     </row>
     <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="10">
+      <c r="A32" s="11">
         <f>IF(B32="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="15">
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="16">
         <f>IF(OR(C32="",E32=""),"",C32*E32)</f>
         <v/>
       </c>
-      <c r="G32" s="16" t="n"/>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="11" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="14" t="n"/>
+      <c r="I32" s="12" t="n"/>
     </row>
     <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="10">
+      <c r="A33" s="11">
         <f>IF(B33="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="15">
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="16">
         <f>IF(OR(C33="",E33=""),"",C33*E33)</f>
         <v/>
       </c>
-      <c r="G33" s="16" t="n"/>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="11" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="14" t="n"/>
+      <c r="I33" s="12" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="10">
+      <c r="A34" s="11">
         <f>IF(B34="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="15">
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="16">
         <f>IF(OR(C34="",E34=""),"",C34*E34)</f>
         <v/>
       </c>
-      <c r="G34" s="16" t="n"/>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="11" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="12" t="n"/>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="10">
+      <c r="A35" s="11">
         <f>IF(B35="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="14" t="n"/>
-      <c r="F35" s="15">
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="16">
         <f>IF(OR(C35="",E35=""),"",C35*E35)</f>
         <v/>
       </c>
-      <c r="G35" s="16" t="n"/>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="11" t="n"/>
+      <c r="G35" s="17" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="12" t="n"/>
     </row>
     <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="10">
+      <c r="A36" s="11">
         <f>IF(B36="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="14" t="n"/>
-      <c r="F36" s="15">
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="14" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="16">
         <f>IF(OR(C36="",E36=""),"",C36*E36)</f>
         <v/>
       </c>
-      <c r="G36" s="16" t="n"/>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="11" t="n"/>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="12" t="n"/>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="10">
+      <c r="A37" s="11">
         <f>IF(B37="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="13" t="n"/>
-      <c r="E37" s="14" t="n"/>
-      <c r="F37" s="15">
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="16">
         <f>IF(OR(C37="",E37=""),"",C37*E37)</f>
         <v/>
       </c>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="11" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="12" t="n"/>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="10">
+      <c r="A38" s="11">
         <f>IF(B38="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="14" t="n"/>
-      <c r="F38" s="15">
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="16">
         <f>IF(OR(C38="",E38=""),"",C38*E38)</f>
         <v/>
       </c>
-      <c r="G38" s="16" t="n"/>
-      <c r="H38" s="13" t="n"/>
-      <c r="I38" s="11" t="n"/>
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="12" t="n"/>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="10">
+      <c r="A39" s="11">
         <f>IF(B39="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="13" t="n"/>
-      <c r="E39" s="14" t="n"/>
-      <c r="F39" s="15">
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="16">
         <f>IF(OR(C39="",E39=""),"",C39*E39)</f>
         <v/>
       </c>
-      <c r="G39" s="16" t="n"/>
-      <c r="H39" s="13" t="n"/>
-      <c r="I39" s="11" t="n"/>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="12" t="n"/>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="10">
+      <c r="A40" s="11">
         <f>IF(B40="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="14" t="n"/>
-      <c r="F40" s="15">
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="16">
         <f>IF(OR(C40="",E40=""),"",C40*E40)</f>
         <v/>
       </c>
-      <c r="G40" s="16" t="n"/>
-      <c r="H40" s="13" t="n"/>
-      <c r="I40" s="11" t="n"/>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="12" t="n"/>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="10">
+      <c r="A41" s="11">
         <f>IF(B41="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="13" t="n"/>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="15">
+      <c r="B41" s="12" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="16">
         <f>IF(OR(C41="",E41=""),"",C41*E41)</f>
         <v/>
       </c>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="13" t="n"/>
-      <c r="I41" s="11" t="n"/>
+      <c r="G41" s="17" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="12" t="n"/>
     </row>
     <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="10">
+      <c r="A42" s="11">
         <f>IF(B42="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="14" t="n"/>
-      <c r="F42" s="15">
+      <c r="B42" s="12" t="n"/>
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="16">
         <f>IF(OR(C42="",E42=""),"",C42*E42)</f>
         <v/>
       </c>
-      <c r="G42" s="16" t="n"/>
-      <c r="H42" s="13" t="n"/>
-      <c r="I42" s="11" t="n"/>
+      <c r="G42" s="17" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="12" t="n"/>
     </row>
     <row r="43" ht="19" customHeight="1">
-      <c r="A43" s="10">
+      <c r="A43" s="11">
         <f>IF(B43="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="14" t="n"/>
-      <c r="F43" s="15">
+      <c r="B43" s="12" t="n"/>
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="16">
         <f>IF(OR(C43="",E43=""),"",C43*E43)</f>
         <v/>
       </c>
-      <c r="G43" s="16" t="n"/>
-      <c r="H43" s="13" t="n"/>
-      <c r="I43" s="11" t="n"/>
+      <c r="G43" s="17" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="12" t="n"/>
     </row>
     <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="10">
+      <c r="A44" s="11">
         <f>IF(B44="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="14" t="n"/>
-      <c r="F44" s="15">
+      <c r="B44" s="12" t="n"/>
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="14" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="16">
         <f>IF(OR(C44="",E44=""),"",C44*E44)</f>
         <v/>
       </c>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="13" t="n"/>
-      <c r="I44" s="11" t="n"/>
+      <c r="G44" s="17" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="12" t="n"/>
     </row>
     <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="10">
+      <c r="A45" s="11">
         <f>IF(B45="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="14" t="n"/>
-      <c r="F45" s="15">
+      <c r="B45" s="12" t="n"/>
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="16">
         <f>IF(OR(C45="",E45=""),"",C45*E45)</f>
         <v/>
       </c>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="13" t="n"/>
-      <c r="I45" s="11" t="n"/>
+      <c r="G45" s="17" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="12" t="n"/>
     </row>
     <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="10">
+      <c r="A46" s="11">
         <f>IF(B46="","",ROW()-11)</f>
         <v/>
       </c>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="15">
+      <c r="B46" s="12" t="n"/>
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="16">
         <f>IF(OR(C46="",E46=""),"",C46*E46)</f>
         <v/>
       </c>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="13" t="n"/>
-      <c r="I46" s="11" t="n"/>
+      <c r="G46" s="17" t="n"/>
+      <c r="H46" s="14" t="n"/>
+      <c r="I46" s="12" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>المجموع الكلي للبنود المسعَّرة (د.أ)</t>
         </is>
       </c>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-      <c r="E47" s="18" t="n"/>
-      <c r="F47" s="19">
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="20">
         <f>SUM(F12:F46)</f>
         <v/>
       </c>
-      <c r="G47" s="20" t="inlineStr">
+      <c r="G47" s="21" t="inlineStr">
         <is>
           <t>البنود بدون سعر تُسعَّر من الكتالوج</t>
         </is>
       </c>
-      <c r="H47" s="18" t="n"/>
-      <c r="I47" s="18" t="n"/>
+      <c r="H47" s="19" t="n"/>
+      <c r="I47" s="19" t="n"/>
     </row>
     <row r="48"/>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>لا تُرسَل الطلبية إلا والحالة النهائية خضراء ✅</t>
         </is>
@@ -1501,7 +1522,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n"/>
-      <c r="H50" s="22" t="inlineStr">
+      <c r="H50" s="23" t="inlineStr">
         <is>
           <t>قرأ الورقة وأدخلها بند بند</t>
         </is>
@@ -1527,7 +1548,7 @@
         </is>
       </c>
       <c r="G51" s="4" t="n"/>
-      <c r="H51" s="22" t="inlineStr">
+      <c r="H51" s="23" t="inlineStr">
         <is>
           <t>قارَنها بالورقة الأصلية بنداً وكميةً</t>
         </is>
@@ -1535,7 +1556,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="G47:I47"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A2:I2"/>
@@ -1547,11 +1568,12 @@
     <mergeCell ref="D9:I9"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="H51:I51"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="E5:I5"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="A6:I6"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="E8:I8"/>
     <mergeCell ref="H50:I50"/>
-    <mergeCell ref="E8:I8"/>
     <mergeCell ref="H3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="E7">
@@ -1621,7 +1643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1636,220 +1658,232 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>أولاً — الموظف اللي بطلّع البضاعة</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>كل طلبية إلها رقم متسلسل. اكتب الرقم على الورقة نفسها قبل أي شي، وافتح ورقة جديدة بالإكسل بنفس الرقم.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>قبل ما تبلّش الإدخال: عُدّ بنود الورقة واكتب العدد بخانة «عدد البنود حسب الأصل». هاي أهم خانة بالنموذج كله.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>أدخل البنود بند بند. وكل بند بتدخله — اشطبه بالقلم على الورقة. أي بند بضل بدون شطب = بند نسيته.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>الكمية رقم فقط. «2 ربطة» تُكتب: الكمية 2 والوحدة «ربطة». لا تكتب الوحدة جوا خانة الكمية.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>تاريخ الإخراج إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>الطلبية الطويلة (فوق 35 بند) تنقسم ورقتين بنفس رقم الطلبية: «الورقة 1 من 2» و«الورقة 2 من 2». كل ورقة بتحمل عدد بنودها هي — مثلاً 35 بالأولى و15 بالثانية — مش عدد الطلبية كلها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>السعر الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه هون مباشرة. إذا تركته فاضي بنسعّره من الكتالوج.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>صوّر الورقة الأصلية واحفظها بنفس رقم الطلبية، وحطّ «نعم» بخانة «صورة الأصل محفوظة».</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>ثانياً — التدقيق (أبو علي)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>التدقيق بصير من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها، وقارن كل سطر بالإكسل.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>لكل بند تتأكد منه (الاسم صح + الكمية صح) حُطّ ✔ بخانة التدقيق.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>العدّاد فوق بيعدّ لحالو. ما بتصير الحالة خضراء إلا لما كل بند يتدقّق وعدد البنود يطابق الورقة.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>وقّع بخانة «دقّقها» وبعدين ابعث الملف + صورة الورقة للأستاذ.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>الضوابط المدمجة بالنموذج</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>«عدد البنود حسب الأصل» ≠ عدد البنود المُدخلة ← بطلع ⛔ أحمر ويقلك كم بند ناقص.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>«مجموع الكميات» (اختياري، موصى به فوق 10 بنود) ← بيمسك الكمية المكتوبة غلط (5 بدل 50).</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>بند مكتوب بدون كمية أو بدون تاريخ ← الخانة بتصير حمرا.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>الخانات الرمادية محسوبة تلقائياً ومقفلة — لا تحاول تعدّلها.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>الفكرة باختصار</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="46" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية، وعشان هيك في شطب بالقلم على الورقة + عدّ مسبق للبنود + شخص تاني بقرأ من الأصل. كل ضابط منهم بمسك الشي اللي الثاني بفوّته.</t>
         </is>
@@ -1857,11 +1891,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/نموذج_طلبية_ورشة.xlsx
+++ b/نموذج_طلبية_ورشة.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'طلبية'!$11:$11</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'طلبية'!$A$1:$I$51</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -767,68 +767,32 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>عدد البنود حسب الأصل</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
+          <t>عدد البنود المُدخلة</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>COUNTA(B12:B46)</f>
+        <v/>
+      </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>المُدخَل فعلياً</t>
+          <t>المدقَّقة ✔</t>
         </is>
       </c>
       <c r="D7" s="8">
-        <f>COUNTA(B12:B46)</f>
-        <v/>
-      </c>
-      <c r="E7" s="8">
-        <f>IF(B7="","— اكتب عدد بنود هاي الورقة أولاً",IF(D7=B7,"✅ مطابق — ما في بند ناقص",IF(D7&lt;B7,"⛔ ناقص "&amp;(B7-D7)&amp;" بند — راجع الورقة","⛔ زائد "&amp;(D7-B7)&amp;" بند — في بند مكرر")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>مجموع الكميات حسب الأصل</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>المُدخَل فعلياً</t>
-        </is>
-      </c>
-      <c r="D8" s="8">
-        <f>SUM(C12:C46)</f>
-        <v/>
-      </c>
-      <c r="E8" s="8">
-        <f>IF(B8="","— اختياري (موصى به للطلبيات فوق 10 بنود)",IF(ROUND(D8,3)=ROUND(B8,3),"✅ مطابق","⛔ فرق "&amp;TEXT(D8-B8,"0.###")&amp;" — في كمية مكتوبة غلط"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>البنود المدقَّقة ✔</t>
-        </is>
-      </c>
-      <c r="B9" s="8">
         <f>COUNTIF(H12:H46,"✔")</f>
         <v/>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>الحالة النهائية</t>
-        </is>
-      </c>
-      <c r="D9" s="9">
-        <f>IF(D7=0,"⛔ ما في بنود مُدخلة",IF(B7="","⛔ ناقص: عدد البنود حسب الأصل",IF(D7&lt;&gt;B7,"⛔ عدد البنود مش مطابق",IF(B9&lt;D7,"⛔ باقي "&amp;(D7-B9)&amp;" بند بدون تدقيق","✅ جاهز للترحيل — ابعثها للأستاذ"))))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="E7" s="9">
+        <f>IF(B7=0,"⛔ ما في بنود مُدخلة",IF(D7&lt;B7,"⛔ باقي "&amp;(B7-D7)&amp;" بند بدون تدقيق — دقّقهن من الورقة الأصلية","✅ كل البنود مدقَّقة — جاهزة للترحيل"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10"/>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
@@ -1556,7 +1520,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="18">
+  <mergeCells count="16">
     <mergeCell ref="G47:I47"/>
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="A2:I2"/>
@@ -1565,14 +1529,12 @@
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="H51:I51"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="H51:I51"/>
     <mergeCell ref="E5:I5"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E8:I8"/>
     <mergeCell ref="H50:I50"/>
     <mergeCell ref="H3:I3"/>
   </mergeCells>
@@ -1584,34 +1546,18 @@
       <formula>LEFT(E7,1)="⛔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>LEFT(E8,1)="✅"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>LEFT(E8,1)="⛔"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9">
-    <cfRule type="expression" priority="5" dxfId="0">
-      <formula>LEFT(D9,1)="✅"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="1">
-      <formula>LEFT(D9,1)="⛔"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C12:C46">
-    <cfRule type="expression" priority="7" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND($B12&lt;&gt;"",$C12="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G12:G46">
-    <cfRule type="expression" priority="8" dxfId="2">
+    <cfRule type="expression" priority="4" dxfId="2">
       <formula>AND($B12&lt;&gt;"",$G12="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12:I46">
-    <cfRule type="expression" priority="9" dxfId="3">
+    <cfRule type="expression" priority="5" dxfId="3">
       <formula>$H12="✔"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1643,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1676,7 +1622,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
           <t>2</t>
@@ -1684,7 +1630,7 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>قبل ما تبلّش الإدخال: عُدّ بنود الورقة واكتب العدد بخانة «عدد البنود حسب الأصل». هاي أهم خانة بالنموذج كله.</t>
+          <t>أدخل البنود بند بند. وكل بند بتدخله — اشطبه بالقلم على الورقة. أي بند بضل بدون شطب = بند نسيته.</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1642,7 @@
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>أدخل البنود بند بند. وكل بند بتدخله — اشطبه بالقلم على الورقة. أي بند بضل بدون شطب = بند نسيته.</t>
+          <t>الكمية رقم فقط. «2 ربطة» تُكتب: الكمية 2 والوحدة «ربطة». لا تكتب الوحدة جوا خانة الكمية.</t>
         </is>
       </c>
     </row>
@@ -1708,11 +1654,11 @@
       </c>
       <c r="B7" s="26" t="inlineStr">
         <is>
-          <t>الكمية رقم فقط. «2 ربطة» تُكتب: الكمية 2 والوحدة «ربطة». لا تكتب الوحدة جوا خانة الكمية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>تاريخ الإخراج إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
           <t>5</t>
@@ -1720,11 +1666,11 @@
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>تاريخ الإخراج إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
+          <t>الطلبية الطويلة (فوق 35 بند) تنقسم ورقتين بنفس رقم الطلبية: «الورقة 1 من 2» و«الورقة 2 من 2». كل ورقة بتحمل عدد بنودها هي — مثلاً 35 بالأولى و15 بالثانية — مش عدد الطلبية كلها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>6</t>
@@ -1732,7 +1678,7 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>الطلبية الطويلة (فوق 35 بند) تنقسم ورقتين بنفس رقم الطلبية: «الورقة 1 من 2» و«الورقة 2 من 2». كل ورقة بتحمل عدد بنودها هي — مثلاً 35 بالأولى و15 بالثانية — مش عدد الطلبية كلها.</t>
+          <t>السعر الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه هون مباشرة. إذا تركته فاضي بنسعّره من الكتالوج.</t>
         </is>
       </c>
     </row>
@@ -1744,26 +1690,26 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>السعر الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه هون مباشرة. إذا تركته فاضي بنسعّره من الكتالوج.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
+          <t>صوّر الورقة الأصلية واحفظها بنفس رقم الطلبية، وحطّ «نعم» بخانة «صورة الأصل محفوظة».</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ثانياً — التدقيق (أبو علي)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
-        <is>
-          <t>صوّر الورقة الأصلية واحفظها بنفس رقم الطلبية، وحطّ «نعم» بخانة «صورة الأصل محفوظة».</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>ثانياً — التدقيق (أبو علي)</t>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>التدقيق بصير من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها، وقارن كل سطر بالإكسل.</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1721,7 @@
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>التدقيق بصير من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها، وقارن كل سطر بالإكسل.</t>
+          <t>لكل بند تتأكد منه (الاسم صح + الكمية صح) حُطّ ✔ بخانة التدقيق.</t>
         </is>
       </c>
     </row>
@@ -1787,7 +1733,7 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>لكل بند تتأكد منه (الاسم صح + الكمية صح) حُطّ ✔ بخانة التدقيق.</t>
+          <t>العدّاد فوق بيعدّ لحالو. ما بتصير الحالة خضراء إلا لما كل بند مُدخل يتأشّر ✔.</t>
         </is>
       </c>
     </row>
@@ -1799,26 +1745,26 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>العدّاد فوق بيعدّ لحالو. ما بتصير الحالة خضراء إلا لما كل بند يتدقّق وعدد البنود يطابق الورقة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
           <t>وقّع بخانة «دقّقها» وبعدين ابعث الملف + صورة الورقة للأستاذ.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>الضوابط المدمجة بالنموذج</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>بند مكتوب بدون كمية أو بدون تاريخ ← الخانة بتصير حمرا.</t>
         </is>
       </c>
     </row>
@@ -1830,72 +1776,36 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>«عدد البنود حسب الأصل» ≠ عدد البنود المُدخلة ← بطلع ⛔ أحمر ويقلك كم بند ناقص.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>«مجموع الكميات» (اختياري، موصى به فوق 10 بنود) ← بيمسك الكمية المكتوبة غلط (5 بدل 50).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t>الخانات الرمادية محسوبة تلقائياً ومقفلة — لا تحاول تعدّلها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>الفكرة باختصار</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>•</t>
+          <t>◆</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>بند مكتوب بدون كمية أو بدون تاريخ ← الخانة بتصير حمرا.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>الخانات الرمادية محسوبة تلقائياً ومقفلة — لا تحاول تعدّلها.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>الفكرة باختصار</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
-      <c r="B23" s="26" t="inlineStr">
-        <is>
-          <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية، وعشان هيك في شطب بالقلم على الورقة + عدّ مسبق للبنود + شخص تاني بقرأ من الأصل. كل ضابط منهم بمسك الشي اللي الثاني بفوّته.</t>
+          <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية، مش مقابل الشاشة: شطب بالقلم على الورقة وقت الإدخال، وشخص تاني بقرأ من الورقة ويأشّر ✔ بند بند.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/نموذج_طلبية_ورشة.xlsx
+++ b/نموذج_طلبية_ورشة.xlsx
@@ -11,9 +11,9 @@
     <sheet name="التعليمات" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'طلبية'!$8:$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'طلبية'!$A$1:$G$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'طلبية'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'طلبية'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,12 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.###"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00555555"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -171,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -183,7 +177,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,32 +197,25 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -640,16 +628,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -659,624 +646,510 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="23" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>الورشة / المشروع</t>
+          <t>الطلبية</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>رقم الطلبية</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n"/>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>المستلِم</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>البنود المُدخلة</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>COUNTA(B7:B41)</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>المدقَّقة</t>
+        </is>
+      </c>
+      <c r="D4" s="5">
+        <f>COUNTA(F7:F41)</f>
+        <v/>
+      </c>
+      <c r="E4" s="6">
+        <f>IF(B4=0,"⛔ ما في بنود مُدخلة",IF(D4&lt;B4,"⛔ باقي "&amp;(B4-D4)&amp;" بند بدون تدقيق","✅ كل البنود مدقَّقة"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>الإفرادي</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="4" t="n"/>
-    </row>
-    <row r="3" ht="23" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>المهندس / المستلِم</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>صورة الأصل محفوظة؟</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>الورقة</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="4" t="n"/>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>البنود المُدخلة</t>
-        </is>
-      </c>
-      <c r="B5" s="5">
-        <f>COUNTA(B9:B43)</f>
-        <v/>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>المدقَّقة</t>
-        </is>
-      </c>
-      <c r="D5" s="5">
-        <f>COUNTA(F9:F43)</f>
-        <v/>
-      </c>
-      <c r="E5" s="6">
-        <f>IF(B5=0,"⛔ ما في بنود مُدخلة",IF(D5&lt;B5,"⛔ باقي "&amp;(B5-D5)&amp;" بند بدون تدقيق","✅ كل البنود مدقَّقة"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>البند</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>الكمية</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>السعر الإفرادي</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>دقّقها</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>ملاحظات</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>المدقق</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="8">
+        <f>IF(B7="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="8">
+        <f>IF(B8="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="8">
-        <f>IF(B9="","",ROW()-8)</f>
+        <f>IF(B9="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="12" t="n"/>
-      <c r="F9" s="13" t="n"/>
-      <c r="G9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
       <c r="A10" s="8">
-        <f>IF(B10="","",ROW()-8)</f>
+        <f>IF(B10="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B10" s="9" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="12" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
+      <c r="F10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
       <c r="A11" s="8">
-        <f>IF(B11="","",ROW()-8)</f>
+        <f>IF(B11="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B11" s="9" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="12" t="n"/>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+      <c r="F11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="8">
-        <f>IF(B12="","",ROW()-8)</f>
+        <f>IF(B12="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B12" s="9" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="12" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
+      <c r="F12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
       <c r="A13" s="8">
-        <f>IF(B13="","",ROW()-8)</f>
+        <f>IF(B13="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B13" s="9" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="12" t="n"/>
-      <c r="F13" s="13" t="n"/>
-      <c r="G13" s="9" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
+      <c r="F13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1">
       <c r="A14" s="8">
-        <f>IF(B14="","",ROW()-8)</f>
+        <f>IF(B14="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B14" s="9" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="12" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
+      <c r="F14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
       <c r="A15" s="8">
-        <f>IF(B15="","",ROW()-8)</f>
+        <f>IF(B15="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B15" s="9" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="12" t="n"/>
-      <c r="F15" s="13" t="n"/>
-      <c r="G15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
+      <c r="F15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
       <c r="A16" s="8">
-        <f>IF(B16="","",ROW()-8)</f>
+        <f>IF(B16="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B16" s="9" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="12" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
+      <c r="F16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
       <c r="A17" s="8">
-        <f>IF(B17="","",ROW()-8)</f>
+        <f>IF(B17="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B17" s="9" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="12" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
+      <c r="F17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
       <c r="A18" s="8">
-        <f>IF(B18="","",ROW()-8)</f>
+        <f>IF(B18="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B18" s="9" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="12" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
+      <c r="F18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
       <c r="A19" s="8">
-        <f>IF(B19="","",ROW()-8)</f>
+        <f>IF(B19="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B19" s="9" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="12" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
+      <c r="F19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
       <c r="A20" s="8">
-        <f>IF(B20="","",ROW()-8)</f>
+        <f>IF(B20="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B20" s="9" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="12" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
+      <c r="F20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
       <c r="A21" s="8">
-        <f>IF(B21="","",ROW()-8)</f>
+        <f>IF(B21="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B21" s="9" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="12" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
+      <c r="F21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
       <c r="A22" s="8">
-        <f>IF(B22="","",ROW()-8)</f>
+        <f>IF(B22="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B22" s="9" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="12" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
+      <c r="F22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
       <c r="A23" s="8">
-        <f>IF(B23="","",ROW()-8)</f>
+        <f>IF(B23="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B23" s="9" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="12" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
+      <c r="F23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
       <c r="A24" s="8">
-        <f>IF(B24="","",ROW()-8)</f>
+        <f>IF(B24="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B24" s="9" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="12" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="8">
-        <f>IF(B25="","",ROW()-8)</f>
+        <f>IF(B25="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B25" s="9" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="12" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="9" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
       <c r="A26" s="8">
-        <f>IF(B26="","",ROW()-8)</f>
+        <f>IF(B26="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B26" s="9" t="n"/>
       <c r="C26" s="10" t="n"/>
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="12" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
+      <c r="F26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
       <c r="A27" s="8">
-        <f>IF(B27="","",ROW()-8)</f>
+        <f>IF(B27="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B27" s="9" t="n"/>
       <c r="C27" s="10" t="n"/>
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
+      <c r="F27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="8">
-        <f>IF(B28="","",ROW()-8)</f>
+        <f>IF(B28="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="12" t="n"/>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
+      <c r="F28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
       <c r="A29" s="8">
-        <f>IF(B29="","",ROW()-8)</f>
+        <f>IF(B29="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B29" s="9" t="n"/>
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="12" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
+      <c r="F29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
       <c r="A30" s="8">
-        <f>IF(B30="","",ROW()-8)</f>
+        <f>IF(B30="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B30" s="9" t="n"/>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="13" t="n"/>
-      <c r="G30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
       <c r="A31" s="8">
-        <f>IF(B31="","",ROW()-8)</f>
+        <f>IF(B31="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B31" s="9" t="n"/>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="12" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
+      <c r="F31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
       <c r="A32" s="8">
-        <f>IF(B32="","",ROW()-8)</f>
+        <f>IF(B32="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B32" s="9" t="n"/>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="12" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="9" t="n"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="21" customHeight="1">
       <c r="A33" s="8">
-        <f>IF(B33="","",ROW()-8)</f>
+        <f>IF(B33="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B33" s="9" t="n"/>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="12" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="9" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="21" customHeight="1">
       <c r="A34" s="8">
-        <f>IF(B34="","",ROW()-8)</f>
+        <f>IF(B34="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="12" t="n"/>
-      <c r="F34" s="13" t="n"/>
-      <c r="G34" s="9" t="n"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="8">
-        <f>IF(B35="","",ROW()-8)</f>
+        <f>IF(B35="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="9" t="n"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="8">
-        <f>IF(B36="","",ROW()-8)</f>
+        <f>IF(B36="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="12" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="9" t="n"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="8">
-        <f>IF(B37="","",ROW()-8)</f>
+        <f>IF(B37="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="13" t="n"/>
-      <c r="G37" s="9" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
       <c r="A38" s="8">
-        <f>IF(B38="","",ROW()-8)</f>
+        <f>IF(B38="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="10" t="n"/>
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="12" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="9" t="n"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
+      <c r="F38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
       <c r="A39" s="8">
-        <f>IF(B39="","",ROW()-8)</f>
+        <f>IF(B39="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="12" t="n"/>
-      <c r="F39" s="13" t="n"/>
-      <c r="G39" s="9" t="n"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="21" customHeight="1">
       <c r="A40" s="8">
-        <f>IF(B40="","",ROW()-8)</f>
+        <f>IF(B40="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B40" s="9" t="n"/>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="12" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="9" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
+      <c r="F40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="21" customHeight="1">
       <c r="A41" s="8">
-        <f>IF(B41="","",ROW()-8)</f>
+        <f>IF(B41="","",ROW()-6)</f>
         <v/>
       </c>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="12" t="n"/>
-      <c r="F41" s="13" t="n"/>
-      <c r="G41" s="9" t="n"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="8">
-        <f>IF(B42="","",ROW()-8)</f>
-        <v/>
-      </c>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="13" t="n"/>
-      <c r="G42" s="9" t="n"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8">
-        <f>IF(B43="","",ROW()-8)</f>
-        <v/>
-      </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="13" t="n"/>
-      <c r="G43" s="9" t="n"/>
-    </row>
-    <row r="44"/>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="14" t="inlineStr">
-        <is>
-          <t>لا تُرسَل الطلبية إلا وكل بند مؤشَّر عليه مدقِّقه</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="25" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>أدخلها</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n"/>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="15" t="inlineStr">
-        <is>
-          <t>نقلها من الورقة الأصلية بند بند</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="25" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>دقّقها</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n"/>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n"/>
-      <c r="E47" s="15" t="inlineStr">
-        <is>
-          <t>قارَنها بالورقة الأصلية: البند صح والعدد صح</t>
+      <c r="F41" s="10" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>لا تُرسَل الطلبية إلا وكل بند مكتوب عليه اسم مدقِّقه</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="7">
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="A45:G45"/>
+  <mergeCells count="3">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5">
+  <conditionalFormatting sqref="E4">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>LEFT(E5,1)="✅"</formula>
+      <formula>LEFT(E4,1)="✅"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>LEFT(E5,1)="⛔"</formula>
+      <formula>LEFT(E4,1)="⛔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:C43">
+  <conditionalFormatting sqref="C7:C41">
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>AND($B9&lt;&gt;"",$C9="")</formula>
+      <formula>AND($B7&lt;&gt;"",$C7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E9:E43">
+  <conditionalFormatting sqref="E7:E41">
     <cfRule type="expression" priority="4" dxfId="2">
-      <formula>AND($B9&lt;&gt;"",$E9="")</formula>
+      <formula>AND($B7&lt;&gt;"",$E7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:G43">
+  <conditionalFormatting sqref="A7:F41">
     <cfRule type="expression" priority="5" dxfId="3">
-      <formula>$F9&lt;&gt;""</formula>
+      <formula>$F7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation sqref="F9:F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="F7:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"عمر المصري,ابو علي"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"عمر المصري,ابو علي"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"نعم,لا"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C9:C43" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="كمية غير صحيحة" error="الكمية رقم فقط. «ربطة» و«جوز» و«لفة» تُكتب بخانة الملاحظات." type="decimal" operator="greaterThan">
-      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1290,7 +1163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1305,153 +1178,129 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>الموظف اللي بطلّع البضاعة</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>ورقة وحدة لكل طلبية، ولها رقم متسلسل. اكتب الرقم على ورقة الطلبية الأصلية كمان.</t>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>ورقة وحدة لكل طلبية. والطلبية الطويلة تنقسم ورقتين.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>أدخل البنود بند بند. وكل بند بتدخله — اشطبه بالقلم على الورقة الأصلية. أي بند بضل بدون شطب = بند نسيته. هاي أهم خطوة بكل النموذج.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>الكمية رقم فقط. «ربطة» و«جوز» و«لفة» تُكتب بخانة الملاحظات.</t>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>التاريخ إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>التاريخ إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه. وإلا اتركه فاضي.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>المدقِّق — عمر المصري أو أبو علي</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>السعر الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه. وإلا اتركه فاضي.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>التدقيق من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>صوّر الورقة الأصلية واحفظها بنفس رقم الطلبية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>المدقِّق — عمر المصري أو أبو علي</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «المدقق» لهذا البند.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>التدقيق من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها.</t>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «دقّقها» لهذا البند.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>وقّع بأسفل الورقة وابعث الملف + صورة الورقة الأصلية للأستاذ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>ابعث الملف + صورة الورقة الأصلية للأستاذ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>الفكرة باختصار</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية لا مقابل الشاشة، ومعه شطب بالقلم على الورقة وقت الإدخال.</t>
         </is>
@@ -1459,10 +1308,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A15:B15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/نموذج_طلبية_ورشة.xlsx
+++ b/نموذج_طلبية_ورشة.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="طلبية" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="الورشة" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="التعليمات" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'طلبية'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'طلبية'!$A$1:$F$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'الورشة'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'الورشة'!$A$1:$G$208</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,12 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -165,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,52 +179,48 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -628,43 +630,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>طلبية ورشة — محلات العون لمواد البناء</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="24" customHeight="1">
+          <t>ورشة — محلات العون لمواد البناء</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>الطلبية</t>
+          <t>الورشة</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>المستلِم</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3"/>
     <row r="4" ht="26" customHeight="1">
@@ -673,8 +664,8 @@
           <t>البنود المُدخلة</t>
         </is>
       </c>
-      <c r="B4" s="5">
-        <f>COUNTA(B7:B41)</f>
+      <c r="B4" s="4">
+        <f>COUNTA(B7:B206)</f>
         <v/>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -682,447 +673,2468 @@
           <t>المدقَّقة</t>
         </is>
       </c>
-      <c r="D4" s="5">
-        <f>COUNTA(F7:F41)</f>
-        <v/>
-      </c>
-      <c r="E4" s="6">
+      <c r="D4" s="4">
+        <f>COUNTA(G7:G206)</f>
+        <v/>
+      </c>
+      <c r="E4" s="5">
         <f>IF(B4=0,"⛔ ما في بنود مُدخلة",IF(D4&lt;B4,"⛔ باقي "&amp;(B4-D4)&amp;" بند بدون تدقيق","✅ كل البنود مدقَّقة"))</f>
         <v/>
       </c>
     </row>
     <row r="5"/>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>الكمية</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>الإفرادي</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>المستلم</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>المدقق</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <f>IF(B7="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="10" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <f>IF(B8="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <f>IF(B9="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="10" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <f>IF(B10="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="10" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <f>IF(B11="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="10" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <f>IF(B12="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="10" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <f>IF(B13="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="10" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <f>IF(B14="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="10" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <f>IF(B15="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="10" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <f>IF(B16="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="10" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <f>IF(B17="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="10" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <f>IF(B18="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="10" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <f>IF(B19="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="10" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="8">
+      <c r="A20" s="7">
         <f>IF(B20="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="10" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <f>IF(B21="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="10" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="8">
+      <c r="A22" s="7">
         <f>IF(B22="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="10" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="8">
+      <c r="A23" s="7">
         <f>IF(B23="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="10" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="8">
+      <c r="A24" s="7">
         <f>IF(B24="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="10" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="8">
+      <c r="A25" s="7">
         <f>IF(B25="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="10" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="8">
+      <c r="A26" s="7">
         <f>IF(B26="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="10" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="8">
+      <c r="A27" s="7">
         <f>IF(B27="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="10" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="8">
+      <c r="A28" s="7">
         <f>IF(B28="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="10" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="8">
+      <c r="A29" s="7">
         <f>IF(B29="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="10" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="8">
+      <c r="A30" s="7">
         <f>IF(B30="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="8">
+      <c r="A31" s="7">
         <f>IF(B31="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="10" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="8">
+      <c r="A32" s="7">
         <f>IF(B32="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="10" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="8">
+      <c r="A33" s="7">
         <f>IF(B33="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="10" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="8">
+      <c r="A34" s="7">
         <f>IF(B34="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="10" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
-      <c r="A35" s="8">
+      <c r="A35" s="7">
         <f>IF(B35="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="8">
+      <c r="A36" s="7">
         <f>IF(B36="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="10" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
-      <c r="A37" s="8">
+      <c r="A37" s="7">
         <f>IF(B37="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
-      <c r="A38" s="8">
+      <c r="A38" s="7">
         <f>IF(B38="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="10" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="A39" s="8">
+      <c r="A39" s="7">
         <f>IF(B39="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="10" t="n"/>
+      <c r="B39" s="8" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
     </row>
     <row r="40" ht="21" customHeight="1">
-      <c r="A40" s="8">
+      <c r="A40" s="7">
         <f>IF(B40="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="10" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
     </row>
     <row r="41" ht="21" customHeight="1">
-      <c r="A41" s="8">
+      <c r="A41" s="7">
         <f>IF(B41="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="10" t="n"/>
-    </row>
-    <row r="42"/>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>لا تُرسَل الطلبية إلا وكل بند مكتوب عليه اسم مدقِّقه</t>
+      <c r="B41" s="8" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="7">
+        <f>IF(B42="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="7">
+        <f>IF(B43="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="7">
+        <f>IF(B44="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="7">
+        <f>IF(B45="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="7">
+        <f>IF(B46="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="A47" s="7">
+        <f>IF(B47="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B47" s="8" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="7">
+        <f>IF(B48="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B48" s="8" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" s="7">
+        <f>IF(B49="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="7">
+        <f>IF(B50="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+    </row>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="7">
+        <f>IF(B51="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="7">
+        <f>IF(B52="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="7">
+        <f>IF(B53="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="11" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="7">
+        <f>IF(B54="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="7">
+        <f>IF(B55="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="7">
+        <f>IF(B56="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="7">
+        <f>IF(B57="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="7">
+        <f>IF(B58="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
+    </row>
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="7">
+        <f>IF(B59="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="7">
+        <f>IF(B60="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="7">
+        <f>IF(B61="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="7">
+        <f>IF(B62="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="9" t="n"/>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="7">
+        <f>IF(B63="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="7">
+        <f>IF(B64="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="9" t="n"/>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="7">
+        <f>IF(B65="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="7">
+        <f>IF(B66="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="7">
+        <f>IF(B67="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="9" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
+    </row>
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" s="7">
+        <f>IF(B68="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="n"/>
+    </row>
+    <row r="69" ht="21" customHeight="1">
+      <c r="A69" s="7">
+        <f>IF(B69="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="n"/>
+    </row>
+    <row r="70" ht="21" customHeight="1">
+      <c r="A70" s="7">
+        <f>IF(B70="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="11" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
+    </row>
+    <row r="71" ht="21" customHeight="1">
+      <c r="A71" s="7">
+        <f>IF(B71="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="9" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="11" t="n"/>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="9" t="n"/>
+    </row>
+    <row r="72" ht="21" customHeight="1">
+      <c r="A72" s="7">
+        <f>IF(B72="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="11" t="n"/>
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="n"/>
+    </row>
+    <row r="73" ht="21" customHeight="1">
+      <c r="A73" s="7">
+        <f>IF(B73="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="11" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="n"/>
+    </row>
+    <row r="74" ht="21" customHeight="1">
+      <c r="A74" s="7">
+        <f>IF(B74="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="11" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n"/>
+    </row>
+    <row r="75" ht="21" customHeight="1">
+      <c r="A75" s="7">
+        <f>IF(B75="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
+    </row>
+    <row r="76" ht="21" customHeight="1">
+      <c r="A76" s="7">
+        <f>IF(B76="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
+    </row>
+    <row r="77" ht="21" customHeight="1">
+      <c r="A77" s="7">
+        <f>IF(B77="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
+    </row>
+    <row r="78" ht="21" customHeight="1">
+      <c r="A78" s="7">
+        <f>IF(B78="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="11" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
+    </row>
+    <row r="79" ht="21" customHeight="1">
+      <c r="A79" s="7">
+        <f>IF(B79="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B79" s="8" t="n"/>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="11" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
+    </row>
+    <row r="80" ht="21" customHeight="1">
+      <c r="A80" s="7">
+        <f>IF(B80="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B80" s="8" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="11" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
+    </row>
+    <row r="81" ht="21" customHeight="1">
+      <c r="A81" s="7">
+        <f>IF(B81="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="11" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
+    </row>
+    <row r="82" ht="21" customHeight="1">
+      <c r="A82" s="7">
+        <f>IF(B82="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="9" t="n"/>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
+    </row>
+    <row r="83" ht="21" customHeight="1">
+      <c r="A83" s="7">
+        <f>IF(B83="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="11" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
+    </row>
+    <row r="84" ht="21" customHeight="1">
+      <c r="A84" s="7">
+        <f>IF(B84="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B84" s="8" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
+    </row>
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" s="7">
+        <f>IF(B85="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
+    </row>
+    <row r="86" ht="21" customHeight="1">
+      <c r="A86" s="7">
+        <f>IF(B86="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="11" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+    </row>
+    <row r="87" ht="21" customHeight="1">
+      <c r="A87" s="7">
+        <f>IF(B87="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B87" s="8" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="11" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" s="7">
+        <f>IF(B88="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B88" s="8" t="n"/>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="11" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+    </row>
+    <row r="89" ht="21" customHeight="1">
+      <c r="A89" s="7">
+        <f>IF(B89="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B89" s="8" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="11" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="7">
+        <f>IF(B90="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="11" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="7">
+        <f>IF(B91="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+    </row>
+    <row r="92" ht="21" customHeight="1">
+      <c r="A92" s="7">
+        <f>IF(B92="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B92" s="8" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+    </row>
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" s="7">
+        <f>IF(B93="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="11" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" s="7">
+        <f>IF(B94="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" s="7">
+        <f>IF(B95="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="7">
+        <f>IF(B96="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B96" s="8" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+    </row>
+    <row r="97" ht="21" customHeight="1">
+      <c r="A97" s="7">
+        <f>IF(B97="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B97" s="8" t="n"/>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" s="7">
+        <f>IF(B98="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B98" s="8" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+    </row>
+    <row r="99" ht="21" customHeight="1">
+      <c r="A99" s="7">
+        <f>IF(B99="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B99" s="8" t="n"/>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="9" t="n"/>
+    </row>
+    <row r="100" ht="21" customHeight="1">
+      <c r="A100" s="7">
+        <f>IF(B100="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
+    </row>
+    <row r="101" ht="21" customHeight="1">
+      <c r="A101" s="7">
+        <f>IF(B101="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B101" s="8" t="n"/>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="11" t="n"/>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="9" t="n"/>
+    </row>
+    <row r="102" ht="21" customHeight="1">
+      <c r="A102" s="7">
+        <f>IF(B102="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="11" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+    </row>
+    <row r="103" ht="21" customHeight="1">
+      <c r="A103" s="7">
+        <f>IF(B103="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="11" t="n"/>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n"/>
+    </row>
+    <row r="104" ht="21" customHeight="1">
+      <c r="A104" s="7">
+        <f>IF(B104="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="11" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+    </row>
+    <row r="105" ht="21" customHeight="1">
+      <c r="A105" s="7">
+        <f>IF(B105="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="11" t="n"/>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="9" t="n"/>
+    </row>
+    <row r="106" ht="21" customHeight="1">
+      <c r="A106" s="7">
+        <f>IF(B106="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B106" s="8" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="11" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+    </row>
+    <row r="107" ht="21" customHeight="1">
+      <c r="A107" s="7">
+        <f>IF(B107="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="11" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="9" t="n"/>
+    </row>
+    <row r="108" ht="21" customHeight="1">
+      <c r="A108" s="7">
+        <f>IF(B108="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B108" s="8" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="11" t="n"/>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="9" t="n"/>
+    </row>
+    <row r="109" ht="21" customHeight="1">
+      <c r="A109" s="7">
+        <f>IF(B109="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B109" s="8" t="n"/>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="11" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="9" t="n"/>
+    </row>
+    <row r="110" ht="21" customHeight="1">
+      <c r="A110" s="7">
+        <f>IF(B110="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="11" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="9" t="n"/>
+    </row>
+    <row r="111" ht="21" customHeight="1">
+      <c r="A111" s="7">
+        <f>IF(B111="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="9" t="n"/>
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="9" t="n"/>
+    </row>
+    <row r="112" ht="21" customHeight="1">
+      <c r="A112" s="7">
+        <f>IF(B112="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B112" s="8" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
+    </row>
+    <row r="113" ht="21" customHeight="1">
+      <c r="A113" s="7">
+        <f>IF(B113="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B113" s="8" t="n"/>
+      <c r="C113" s="9" t="n"/>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="11" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
+    </row>
+    <row r="114" ht="21" customHeight="1">
+      <c r="A114" s="7">
+        <f>IF(B114="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B114" s="8" t="n"/>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="11" t="n"/>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="9" t="n"/>
+    </row>
+    <row r="115" ht="21" customHeight="1">
+      <c r="A115" s="7">
+        <f>IF(B115="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="11" t="n"/>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="9" t="n"/>
+    </row>
+    <row r="116" ht="21" customHeight="1">
+      <c r="A116" s="7">
+        <f>IF(B116="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="11" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="9" t="n"/>
+    </row>
+    <row r="117" ht="21" customHeight="1">
+      <c r="A117" s="7">
+        <f>IF(B117="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B117" s="8" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="11" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
+    </row>
+    <row r="118" ht="21" customHeight="1">
+      <c r="A118" s="7">
+        <f>IF(B118="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B118" s="8" t="n"/>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="11" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="9" t="n"/>
+    </row>
+    <row r="119" ht="21" customHeight="1">
+      <c r="A119" s="7">
+        <f>IF(B119="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B119" s="8" t="n"/>
+      <c r="C119" s="9" t="n"/>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="11" t="n"/>
+      <c r="F119" s="9" t="n"/>
+      <c r="G119" s="9" t="n"/>
+    </row>
+    <row r="120" ht="21" customHeight="1">
+      <c r="A120" s="7">
+        <f>IF(B120="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B120" s="8" t="n"/>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="11" t="n"/>
+      <c r="F120" s="9" t="n"/>
+      <c r="G120" s="9" t="n"/>
+    </row>
+    <row r="121" ht="21" customHeight="1">
+      <c r="A121" s="7">
+        <f>IF(B121="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B121" s="8" t="n"/>
+      <c r="C121" s="9" t="n"/>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="11" t="n"/>
+      <c r="F121" s="9" t="n"/>
+      <c r="G121" s="9" t="n"/>
+    </row>
+    <row r="122" ht="21" customHeight="1">
+      <c r="A122" s="7">
+        <f>IF(B122="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="11" t="n"/>
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="9" t="n"/>
+    </row>
+    <row r="123" ht="21" customHeight="1">
+      <c r="A123" s="7">
+        <f>IF(B123="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B123" s="8" t="n"/>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="11" t="n"/>
+      <c r="F123" s="9" t="n"/>
+      <c r="G123" s="9" t="n"/>
+    </row>
+    <row r="124" ht="21" customHeight="1">
+      <c r="A124" s="7">
+        <f>IF(B124="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B124" s="8" t="n"/>
+      <c r="C124" s="9" t="n"/>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="11" t="n"/>
+      <c r="F124" s="9" t="n"/>
+      <c r="G124" s="9" t="n"/>
+    </row>
+    <row r="125" ht="21" customHeight="1">
+      <c r="A125" s="7">
+        <f>IF(B125="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="9" t="n"/>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="11" t="n"/>
+      <c r="F125" s="9" t="n"/>
+      <c r="G125" s="9" t="n"/>
+    </row>
+    <row r="126" ht="21" customHeight="1">
+      <c r="A126" s="7">
+        <f>IF(B126="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="11" t="n"/>
+      <c r="F126" s="9" t="n"/>
+      <c r="G126" s="9" t="n"/>
+    </row>
+    <row r="127" ht="21" customHeight="1">
+      <c r="A127" s="7">
+        <f>IF(B127="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B127" s="8" t="n"/>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="11" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="9" t="n"/>
+    </row>
+    <row r="128" ht="21" customHeight="1">
+      <c r="A128" s="7">
+        <f>IF(B128="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B128" s="8" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="11" t="n"/>
+      <c r="F128" s="9" t="n"/>
+      <c r="G128" s="9" t="n"/>
+    </row>
+    <row r="129" ht="21" customHeight="1">
+      <c r="A129" s="7">
+        <f>IF(B129="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B129" s="8" t="n"/>
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="11" t="n"/>
+      <c r="F129" s="9" t="n"/>
+      <c r="G129" s="9" t="n"/>
+    </row>
+    <row r="130" ht="21" customHeight="1">
+      <c r="A130" s="7">
+        <f>IF(B130="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B130" s="8" t="n"/>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="11" t="n"/>
+      <c r="F130" s="9" t="n"/>
+      <c r="G130" s="9" t="n"/>
+    </row>
+    <row r="131" ht="21" customHeight="1">
+      <c r="A131" s="7">
+        <f>IF(B131="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="11" t="n"/>
+      <c r="F131" s="9" t="n"/>
+      <c r="G131" s="9" t="n"/>
+    </row>
+    <row r="132" ht="21" customHeight="1">
+      <c r="A132" s="7">
+        <f>IF(B132="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B132" s="8" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="11" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="9" t="n"/>
+    </row>
+    <row r="133" ht="21" customHeight="1">
+      <c r="A133" s="7">
+        <f>IF(B133="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B133" s="8" t="n"/>
+      <c r="C133" s="9" t="n"/>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="11" t="n"/>
+      <c r="F133" s="9" t="n"/>
+      <c r="G133" s="9" t="n"/>
+    </row>
+    <row r="134" ht="21" customHeight="1">
+      <c r="A134" s="7">
+        <f>IF(B134="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B134" s="8" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="11" t="n"/>
+      <c r="F134" s="9" t="n"/>
+      <c r="G134" s="9" t="n"/>
+    </row>
+    <row r="135" ht="21" customHeight="1">
+      <c r="A135" s="7">
+        <f>IF(B135="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B135" s="8" t="n"/>
+      <c r="C135" s="9" t="n"/>
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="9" t="n"/>
+      <c r="G135" s="9" t="n"/>
+    </row>
+    <row r="136" ht="21" customHeight="1">
+      <c r="A136" s="7">
+        <f>IF(B136="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="9" t="n"/>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="9" t="n"/>
+      <c r="G136" s="9" t="n"/>
+    </row>
+    <row r="137" ht="21" customHeight="1">
+      <c r="A137" s="7">
+        <f>IF(B137="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B137" s="8" t="n"/>
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="11" t="n"/>
+      <c r="F137" s="9" t="n"/>
+      <c r="G137" s="9" t="n"/>
+    </row>
+    <row r="138" ht="21" customHeight="1">
+      <c r="A138" s="7">
+        <f>IF(B138="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B138" s="8" t="n"/>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="11" t="n"/>
+      <c r="F138" s="9" t="n"/>
+      <c r="G138" s="9" t="n"/>
+    </row>
+    <row r="139" ht="21" customHeight="1">
+      <c r="A139" s="7">
+        <f>IF(B139="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B139" s="8" t="n"/>
+      <c r="C139" s="9" t="n"/>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="11" t="n"/>
+      <c r="F139" s="9" t="n"/>
+      <c r="G139" s="9" t="n"/>
+    </row>
+    <row r="140" ht="21" customHeight="1">
+      <c r="A140" s="7">
+        <f>IF(B140="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B140" s="8" t="n"/>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="11" t="n"/>
+      <c r="F140" s="9" t="n"/>
+      <c r="G140" s="9" t="n"/>
+    </row>
+    <row r="141" ht="21" customHeight="1">
+      <c r="A141" s="7">
+        <f>IF(B141="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B141" s="8" t="n"/>
+      <c r="C141" s="9" t="n"/>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="11" t="n"/>
+      <c r="F141" s="9" t="n"/>
+      <c r="G141" s="9" t="n"/>
+    </row>
+    <row r="142" ht="21" customHeight="1">
+      <c r="A142" s="7">
+        <f>IF(B142="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B142" s="8" t="n"/>
+      <c r="C142" s="9" t="n"/>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="11" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
+    </row>
+    <row r="143" ht="21" customHeight="1">
+      <c r="A143" s="7">
+        <f>IF(B143="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B143" s="8" t="n"/>
+      <c r="C143" s="9" t="n"/>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="11" t="n"/>
+      <c r="F143" s="9" t="n"/>
+      <c r="G143" s="9" t="n"/>
+    </row>
+    <row r="144" ht="21" customHeight="1">
+      <c r="A144" s="7">
+        <f>IF(B144="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B144" s="8" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="11" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
+    </row>
+    <row r="145" ht="21" customHeight="1">
+      <c r="A145" s="7">
+        <f>IF(B145="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B145" s="8" t="n"/>
+      <c r="C145" s="9" t="n"/>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="9" t="n"/>
+      <c r="G145" s="9" t="n"/>
+    </row>
+    <row r="146" ht="21" customHeight="1">
+      <c r="A146" s="7">
+        <f>IF(B146="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="11" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="9" t="n"/>
+    </row>
+    <row r="147" ht="21" customHeight="1">
+      <c r="A147" s="7">
+        <f>IF(B147="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B147" s="8" t="n"/>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="11" t="n"/>
+      <c r="F147" s="9" t="n"/>
+      <c r="G147" s="9" t="n"/>
+    </row>
+    <row r="148" ht="21" customHeight="1">
+      <c r="A148" s="7">
+        <f>IF(B148="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B148" s="8" t="n"/>
+      <c r="C148" s="9" t="n"/>
+      <c r="D148" s="10" t="n"/>
+      <c r="E148" s="11" t="n"/>
+      <c r="F148" s="9" t="n"/>
+      <c r="G148" s="9" t="n"/>
+    </row>
+    <row r="149" ht="21" customHeight="1">
+      <c r="A149" s="7">
+        <f>IF(B149="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B149" s="8" t="n"/>
+      <c r="C149" s="9" t="n"/>
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="11" t="n"/>
+      <c r="F149" s="9" t="n"/>
+      <c r="G149" s="9" t="n"/>
+    </row>
+    <row r="150" ht="21" customHeight="1">
+      <c r="A150" s="7">
+        <f>IF(B150="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B150" s="8" t="n"/>
+      <c r="C150" s="9" t="n"/>
+      <c r="D150" s="10" t="n"/>
+      <c r="E150" s="11" t="n"/>
+      <c r="F150" s="9" t="n"/>
+      <c r="G150" s="9" t="n"/>
+    </row>
+    <row r="151" ht="21" customHeight="1">
+      <c r="A151" s="7">
+        <f>IF(B151="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B151" s="8" t="n"/>
+      <c r="C151" s="9" t="n"/>
+      <c r="D151" s="10" t="n"/>
+      <c r="E151" s="11" t="n"/>
+      <c r="F151" s="9" t="n"/>
+      <c r="G151" s="9" t="n"/>
+    </row>
+    <row r="152" ht="21" customHeight="1">
+      <c r="A152" s="7">
+        <f>IF(B152="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B152" s="8" t="n"/>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="10" t="n"/>
+      <c r="E152" s="11" t="n"/>
+      <c r="F152" s="9" t="n"/>
+      <c r="G152" s="9" t="n"/>
+    </row>
+    <row r="153" ht="21" customHeight="1">
+      <c r="A153" s="7">
+        <f>IF(B153="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="9" t="n"/>
+      <c r="D153" s="10" t="n"/>
+      <c r="E153" s="11" t="n"/>
+      <c r="F153" s="9" t="n"/>
+      <c r="G153" s="9" t="n"/>
+    </row>
+    <row r="154" ht="21" customHeight="1">
+      <c r="A154" s="7">
+        <f>IF(B154="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B154" s="8" t="n"/>
+      <c r="C154" s="9" t="n"/>
+      <c r="D154" s="10" t="n"/>
+      <c r="E154" s="11" t="n"/>
+      <c r="F154" s="9" t="n"/>
+      <c r="G154" s="9" t="n"/>
+    </row>
+    <row r="155" ht="21" customHeight="1">
+      <c r="A155" s="7">
+        <f>IF(B155="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="11" t="n"/>
+      <c r="F155" s="9" t="n"/>
+      <c r="G155" s="9" t="n"/>
+    </row>
+    <row r="156" ht="21" customHeight="1">
+      <c r="A156" s="7">
+        <f>IF(B156="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B156" s="8" t="n"/>
+      <c r="C156" s="9" t="n"/>
+      <c r="D156" s="10" t="n"/>
+      <c r="E156" s="11" t="n"/>
+      <c r="F156" s="9" t="n"/>
+      <c r="G156" s="9" t="n"/>
+    </row>
+    <row r="157" ht="21" customHeight="1">
+      <c r="A157" s="7">
+        <f>IF(B157="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B157" s="8" t="n"/>
+      <c r="C157" s="9" t="n"/>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="11" t="n"/>
+      <c r="F157" s="9" t="n"/>
+      <c r="G157" s="9" t="n"/>
+    </row>
+    <row r="158" ht="21" customHeight="1">
+      <c r="A158" s="7">
+        <f>IF(B158="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B158" s="8" t="n"/>
+      <c r="C158" s="9" t="n"/>
+      <c r="D158" s="10" t="n"/>
+      <c r="E158" s="11" t="n"/>
+      <c r="F158" s="9" t="n"/>
+      <c r="G158" s="9" t="n"/>
+    </row>
+    <row r="159" ht="21" customHeight="1">
+      <c r="A159" s="7">
+        <f>IF(B159="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B159" s="8" t="n"/>
+      <c r="C159" s="9" t="n"/>
+      <c r="D159" s="10" t="n"/>
+      <c r="E159" s="11" t="n"/>
+      <c r="F159" s="9" t="n"/>
+      <c r="G159" s="9" t="n"/>
+    </row>
+    <row r="160" ht="21" customHeight="1">
+      <c r="A160" s="7">
+        <f>IF(B160="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B160" s="8" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="11" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="9" t="n"/>
+    </row>
+    <row r="161" ht="21" customHeight="1">
+      <c r="A161" s="7">
+        <f>IF(B161="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B161" s="8" t="n"/>
+      <c r="C161" s="9" t="n"/>
+      <c r="D161" s="10" t="n"/>
+      <c r="E161" s="11" t="n"/>
+      <c r="F161" s="9" t="n"/>
+      <c r="G161" s="9" t="n"/>
+    </row>
+    <row r="162" ht="21" customHeight="1">
+      <c r="A162" s="7">
+        <f>IF(B162="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B162" s="8" t="n"/>
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="10" t="n"/>
+      <c r="E162" s="11" t="n"/>
+      <c r="F162" s="9" t="n"/>
+      <c r="G162" s="9" t="n"/>
+    </row>
+    <row r="163" ht="21" customHeight="1">
+      <c r="A163" s="7">
+        <f>IF(B163="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B163" s="8" t="n"/>
+      <c r="C163" s="9" t="n"/>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="11" t="n"/>
+      <c r="F163" s="9" t="n"/>
+      <c r="G163" s="9" t="n"/>
+    </row>
+    <row r="164" ht="21" customHeight="1">
+      <c r="A164" s="7">
+        <f>IF(B164="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B164" s="8" t="n"/>
+      <c r="C164" s="9" t="n"/>
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="11" t="n"/>
+      <c r="F164" s="9" t="n"/>
+      <c r="G164" s="9" t="n"/>
+    </row>
+    <row r="165" ht="21" customHeight="1">
+      <c r="A165" s="7">
+        <f>IF(B165="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B165" s="8" t="n"/>
+      <c r="C165" s="9" t="n"/>
+      <c r="D165" s="10" t="n"/>
+      <c r="E165" s="11" t="n"/>
+      <c r="F165" s="9" t="n"/>
+      <c r="G165" s="9" t="n"/>
+    </row>
+    <row r="166" ht="21" customHeight="1">
+      <c r="A166" s="7">
+        <f>IF(B166="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B166" s="8" t="n"/>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="10" t="n"/>
+      <c r="E166" s="11" t="n"/>
+      <c r="F166" s="9" t="n"/>
+      <c r="G166" s="9" t="n"/>
+    </row>
+    <row r="167" ht="21" customHeight="1">
+      <c r="A167" s="7">
+        <f>IF(B167="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B167" s="8" t="n"/>
+      <c r="C167" s="9" t="n"/>
+      <c r="D167" s="10" t="n"/>
+      <c r="E167" s="11" t="n"/>
+      <c r="F167" s="9" t="n"/>
+      <c r="G167" s="9" t="n"/>
+    </row>
+    <row r="168" ht="21" customHeight="1">
+      <c r="A168" s="7">
+        <f>IF(B168="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B168" s="8" t="n"/>
+      <c r="C168" s="9" t="n"/>
+      <c r="D168" s="10" t="n"/>
+      <c r="E168" s="11" t="n"/>
+      <c r="F168" s="9" t="n"/>
+      <c r="G168" s="9" t="n"/>
+    </row>
+    <row r="169" ht="21" customHeight="1">
+      <c r="A169" s="7">
+        <f>IF(B169="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B169" s="8" t="n"/>
+      <c r="C169" s="9" t="n"/>
+      <c r="D169" s="10" t="n"/>
+      <c r="E169" s="11" t="n"/>
+      <c r="F169" s="9" t="n"/>
+      <c r="G169" s="9" t="n"/>
+    </row>
+    <row r="170" ht="21" customHeight="1">
+      <c r="A170" s="7">
+        <f>IF(B170="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B170" s="8" t="n"/>
+      <c r="C170" s="9" t="n"/>
+      <c r="D170" s="10" t="n"/>
+      <c r="E170" s="11" t="n"/>
+      <c r="F170" s="9" t="n"/>
+      <c r="G170" s="9" t="n"/>
+    </row>
+    <row r="171" ht="21" customHeight="1">
+      <c r="A171" s="7">
+        <f>IF(B171="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B171" s="8" t="n"/>
+      <c r="C171" s="9" t="n"/>
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="11" t="n"/>
+      <c r="F171" s="9" t="n"/>
+      <c r="G171" s="9" t="n"/>
+    </row>
+    <row r="172" ht="21" customHeight="1">
+      <c r="A172" s="7">
+        <f>IF(B172="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B172" s="8" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="10" t="n"/>
+      <c r="E172" s="11" t="n"/>
+      <c r="F172" s="9" t="n"/>
+      <c r="G172" s="9" t="n"/>
+    </row>
+    <row r="173" ht="21" customHeight="1">
+      <c r="A173" s="7">
+        <f>IF(B173="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="9" t="n"/>
+      <c r="D173" s="10" t="n"/>
+      <c r="E173" s="11" t="n"/>
+      <c r="F173" s="9" t="n"/>
+      <c r="G173" s="9" t="n"/>
+    </row>
+    <row r="174" ht="21" customHeight="1">
+      <c r="A174" s="7">
+        <f>IF(B174="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B174" s="8" t="n"/>
+      <c r="C174" s="9" t="n"/>
+      <c r="D174" s="10" t="n"/>
+      <c r="E174" s="11" t="n"/>
+      <c r="F174" s="9" t="n"/>
+      <c r="G174" s="9" t="n"/>
+    </row>
+    <row r="175" ht="21" customHeight="1">
+      <c r="A175" s="7">
+        <f>IF(B175="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B175" s="8" t="n"/>
+      <c r="C175" s="9" t="n"/>
+      <c r="D175" s="10" t="n"/>
+      <c r="E175" s="11" t="n"/>
+      <c r="F175" s="9" t="n"/>
+      <c r="G175" s="9" t="n"/>
+    </row>
+    <row r="176" ht="21" customHeight="1">
+      <c r="A176" s="7">
+        <f>IF(B176="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B176" s="8" t="n"/>
+      <c r="C176" s="9" t="n"/>
+      <c r="D176" s="10" t="n"/>
+      <c r="E176" s="11" t="n"/>
+      <c r="F176" s="9" t="n"/>
+      <c r="G176" s="9" t="n"/>
+    </row>
+    <row r="177" ht="21" customHeight="1">
+      <c r="A177" s="7">
+        <f>IF(B177="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B177" s="8" t="n"/>
+      <c r="C177" s="9" t="n"/>
+      <c r="D177" s="10" t="n"/>
+      <c r="E177" s="11" t="n"/>
+      <c r="F177" s="9" t="n"/>
+      <c r="G177" s="9" t="n"/>
+    </row>
+    <row r="178" ht="21" customHeight="1">
+      <c r="A178" s="7">
+        <f>IF(B178="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B178" s="8" t="n"/>
+      <c r="C178" s="9" t="n"/>
+      <c r="D178" s="10" t="n"/>
+      <c r="E178" s="11" t="n"/>
+      <c r="F178" s="9" t="n"/>
+      <c r="G178" s="9" t="n"/>
+    </row>
+    <row r="179" ht="21" customHeight="1">
+      <c r="A179" s="7">
+        <f>IF(B179="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B179" s="8" t="n"/>
+      <c r="C179" s="9" t="n"/>
+      <c r="D179" s="10" t="n"/>
+      <c r="E179" s="11" t="n"/>
+      <c r="F179" s="9" t="n"/>
+      <c r="G179" s="9" t="n"/>
+    </row>
+    <row r="180" ht="21" customHeight="1">
+      <c r="A180" s="7">
+        <f>IF(B180="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B180" s="8" t="n"/>
+      <c r="C180" s="9" t="n"/>
+      <c r="D180" s="10" t="n"/>
+      <c r="E180" s="11" t="n"/>
+      <c r="F180" s="9" t="n"/>
+      <c r="G180" s="9" t="n"/>
+    </row>
+    <row r="181" ht="21" customHeight="1">
+      <c r="A181" s="7">
+        <f>IF(B181="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B181" s="8" t="n"/>
+      <c r="C181" s="9" t="n"/>
+      <c r="D181" s="10" t="n"/>
+      <c r="E181" s="11" t="n"/>
+      <c r="F181" s="9" t="n"/>
+      <c r="G181" s="9" t="n"/>
+    </row>
+    <row r="182" ht="21" customHeight="1">
+      <c r="A182" s="7">
+        <f>IF(B182="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B182" s="8" t="n"/>
+      <c r="C182" s="9" t="n"/>
+      <c r="D182" s="10" t="n"/>
+      <c r="E182" s="11" t="n"/>
+      <c r="F182" s="9" t="n"/>
+      <c r="G182" s="9" t="n"/>
+    </row>
+    <row r="183" ht="21" customHeight="1">
+      <c r="A183" s="7">
+        <f>IF(B183="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B183" s="8" t="n"/>
+      <c r="C183" s="9" t="n"/>
+      <c r="D183" s="10" t="n"/>
+      <c r="E183" s="11" t="n"/>
+      <c r="F183" s="9" t="n"/>
+      <c r="G183" s="9" t="n"/>
+    </row>
+    <row r="184" ht="21" customHeight="1">
+      <c r="A184" s="7">
+        <f>IF(B184="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B184" s="8" t="n"/>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="10" t="n"/>
+      <c r="E184" s="11" t="n"/>
+      <c r="F184" s="9" t="n"/>
+      <c r="G184" s="9" t="n"/>
+    </row>
+    <row r="185" ht="21" customHeight="1">
+      <c r="A185" s="7">
+        <f>IF(B185="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B185" s="8" t="n"/>
+      <c r="C185" s="9" t="n"/>
+      <c r="D185" s="10" t="n"/>
+      <c r="E185" s="11" t="n"/>
+      <c r="F185" s="9" t="n"/>
+      <c r="G185" s="9" t="n"/>
+    </row>
+    <row r="186" ht="21" customHeight="1">
+      <c r="A186" s="7">
+        <f>IF(B186="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B186" s="8" t="n"/>
+      <c r="C186" s="9" t="n"/>
+      <c r="D186" s="10" t="n"/>
+      <c r="E186" s="11" t="n"/>
+      <c r="F186" s="9" t="n"/>
+      <c r="G186" s="9" t="n"/>
+    </row>
+    <row r="187" ht="21" customHeight="1">
+      <c r="A187" s="7">
+        <f>IF(B187="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B187" s="8" t="n"/>
+      <c r="C187" s="9" t="n"/>
+      <c r="D187" s="10" t="n"/>
+      <c r="E187" s="11" t="n"/>
+      <c r="F187" s="9" t="n"/>
+      <c r="G187" s="9" t="n"/>
+    </row>
+    <row r="188" ht="21" customHeight="1">
+      <c r="A188" s="7">
+        <f>IF(B188="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B188" s="8" t="n"/>
+      <c r="C188" s="9" t="n"/>
+      <c r="D188" s="10" t="n"/>
+      <c r="E188" s="11" t="n"/>
+      <c r="F188" s="9" t="n"/>
+      <c r="G188" s="9" t="n"/>
+    </row>
+    <row r="189" ht="21" customHeight="1">
+      <c r="A189" s="7">
+        <f>IF(B189="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B189" s="8" t="n"/>
+      <c r="C189" s="9" t="n"/>
+      <c r="D189" s="10" t="n"/>
+      <c r="E189" s="11" t="n"/>
+      <c r="F189" s="9" t="n"/>
+      <c r="G189" s="9" t="n"/>
+    </row>
+    <row r="190" ht="21" customHeight="1">
+      <c r="A190" s="7">
+        <f>IF(B190="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B190" s="8" t="n"/>
+      <c r="C190" s="9" t="n"/>
+      <c r="D190" s="10" t="n"/>
+      <c r="E190" s="11" t="n"/>
+      <c r="F190" s="9" t="n"/>
+      <c r="G190" s="9" t="n"/>
+    </row>
+    <row r="191" ht="21" customHeight="1">
+      <c r="A191" s="7">
+        <f>IF(B191="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B191" s="8" t="n"/>
+      <c r="C191" s="9" t="n"/>
+      <c r="D191" s="10" t="n"/>
+      <c r="E191" s="11" t="n"/>
+      <c r="F191" s="9" t="n"/>
+      <c r="G191" s="9" t="n"/>
+    </row>
+    <row r="192" ht="21" customHeight="1">
+      <c r="A192" s="7">
+        <f>IF(B192="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B192" s="8" t="n"/>
+      <c r="C192" s="9" t="n"/>
+      <c r="D192" s="10" t="n"/>
+      <c r="E192" s="11" t="n"/>
+      <c r="F192" s="9" t="n"/>
+      <c r="G192" s="9" t="n"/>
+    </row>
+    <row r="193" ht="21" customHeight="1">
+      <c r="A193" s="7">
+        <f>IF(B193="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B193" s="8" t="n"/>
+      <c r="C193" s="9" t="n"/>
+      <c r="D193" s="10" t="n"/>
+      <c r="E193" s="11" t="n"/>
+      <c r="F193" s="9" t="n"/>
+      <c r="G193" s="9" t="n"/>
+    </row>
+    <row r="194" ht="21" customHeight="1">
+      <c r="A194" s="7">
+        <f>IF(B194="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="9" t="n"/>
+      <c r="D194" s="10" t="n"/>
+      <c r="E194" s="11" t="n"/>
+      <c r="F194" s="9" t="n"/>
+      <c r="G194" s="9" t="n"/>
+    </row>
+    <row r="195" ht="21" customHeight="1">
+      <c r="A195" s="7">
+        <f>IF(B195="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B195" s="8" t="n"/>
+      <c r="C195" s="9" t="n"/>
+      <c r="D195" s="10" t="n"/>
+      <c r="E195" s="11" t="n"/>
+      <c r="F195" s="9" t="n"/>
+      <c r="G195" s="9" t="n"/>
+    </row>
+    <row r="196" ht="21" customHeight="1">
+      <c r="A196" s="7">
+        <f>IF(B196="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B196" s="8" t="n"/>
+      <c r="C196" s="9" t="n"/>
+      <c r="D196" s="10" t="n"/>
+      <c r="E196" s="11" t="n"/>
+      <c r="F196" s="9" t="n"/>
+      <c r="G196" s="9" t="n"/>
+    </row>
+    <row r="197" ht="21" customHeight="1">
+      <c r="A197" s="7">
+        <f>IF(B197="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B197" s="8" t="n"/>
+      <c r="C197" s="9" t="n"/>
+      <c r="D197" s="10" t="n"/>
+      <c r="E197" s="11" t="n"/>
+      <c r="F197" s="9" t="n"/>
+      <c r="G197" s="9" t="n"/>
+    </row>
+    <row r="198" ht="21" customHeight="1">
+      <c r="A198" s="7">
+        <f>IF(B198="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B198" s="8" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="10" t="n"/>
+      <c r="E198" s="11" t="n"/>
+      <c r="F198" s="9" t="n"/>
+      <c r="G198" s="9" t="n"/>
+    </row>
+    <row r="199" ht="21" customHeight="1">
+      <c r="A199" s="7">
+        <f>IF(B199="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B199" s="8" t="n"/>
+      <c r="C199" s="9" t="n"/>
+      <c r="D199" s="10" t="n"/>
+      <c r="E199" s="11" t="n"/>
+      <c r="F199" s="9" t="n"/>
+      <c r="G199" s="9" t="n"/>
+    </row>
+    <row r="200" ht="21" customHeight="1">
+      <c r="A200" s="7">
+        <f>IF(B200="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B200" s="8" t="n"/>
+      <c r="C200" s="9" t="n"/>
+      <c r="D200" s="10" t="n"/>
+      <c r="E200" s="11" t="n"/>
+      <c r="F200" s="9" t="n"/>
+      <c r="G200" s="9" t="n"/>
+    </row>
+    <row r="201" ht="21" customHeight="1">
+      <c r="A201" s="7">
+        <f>IF(B201="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B201" s="8" t="n"/>
+      <c r="C201" s="9" t="n"/>
+      <c r="D201" s="10" t="n"/>
+      <c r="E201" s="11" t="n"/>
+      <c r="F201" s="9" t="n"/>
+      <c r="G201" s="9" t="n"/>
+    </row>
+    <row r="202" ht="21" customHeight="1">
+      <c r="A202" s="7">
+        <f>IF(B202="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B202" s="8" t="n"/>
+      <c r="C202" s="9" t="n"/>
+      <c r="D202" s="10" t="n"/>
+      <c r="E202" s="11" t="n"/>
+      <c r="F202" s="9" t="n"/>
+      <c r="G202" s="9" t="n"/>
+    </row>
+    <row r="203" ht="21" customHeight="1">
+      <c r="A203" s="7">
+        <f>IF(B203="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B203" s="8" t="n"/>
+      <c r="C203" s="9" t="n"/>
+      <c r="D203" s="10" t="n"/>
+      <c r="E203" s="11" t="n"/>
+      <c r="F203" s="9" t="n"/>
+      <c r="G203" s="9" t="n"/>
+    </row>
+    <row r="204" ht="21" customHeight="1">
+      <c r="A204" s="7">
+        <f>IF(B204="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B204" s="8" t="n"/>
+      <c r="C204" s="9" t="n"/>
+      <c r="D204" s="10" t="n"/>
+      <c r="E204" s="11" t="n"/>
+      <c r="F204" s="9" t="n"/>
+      <c r="G204" s="9" t="n"/>
+    </row>
+    <row r="205" ht="21" customHeight="1">
+      <c r="A205" s="7">
+        <f>IF(B205="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B205" s="8" t="n"/>
+      <c r="C205" s="9" t="n"/>
+      <c r="D205" s="10" t="n"/>
+      <c r="E205" s="11" t="n"/>
+      <c r="F205" s="9" t="n"/>
+      <c r="G205" s="9" t="n"/>
+    </row>
+    <row r="206" ht="21" customHeight="1">
+      <c r="A206" s="7">
+        <f>IF(B206="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B206" s="8" t="n"/>
+      <c r="C206" s="9" t="n"/>
+      <c r="D206" s="10" t="n"/>
+      <c r="E206" s="11" t="n"/>
+      <c r="F206" s="9" t="n"/>
+      <c r="G206" s="9" t="n"/>
+    </row>
+    <row r="207"/>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="12" t="inlineStr">
+        <is>
+          <t>لا يُرسَل الملف إلا وكل بند مكتوب عليه اسم مدقِّقه</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
-  <mergeCells count="3">
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A43:F43"/>
+  <mergeCells count="4">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A208:G208"/>
   </mergeCells>
   <conditionalFormatting sqref="E4">
     <cfRule type="expression" priority="1" dxfId="0">
@@ -1132,23 +3144,23 @@
       <formula>LEFT(E4,1)="⛔"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:C41">
+  <conditionalFormatting sqref="C7:C206">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>AND($B7&lt;&gt;"",$C7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:E41">
+  <conditionalFormatting sqref="E7:E206">
     <cfRule type="expression" priority="4" dxfId="2">
       <formula>AND($B7&lt;&gt;"",$E7="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:F41">
+  <conditionalFormatting sqref="A7:G206">
     <cfRule type="expression" priority="5" dxfId="3">
-      <formula>$F7&lt;&gt;""</formula>
+      <formula>$G7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F7:F41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G7:G206" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"عمر المصري,ابو علي"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1163,7 +3175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1178,129 +3190,153 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>الموظف اللي بطلّع البضاعة</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>ورقة وحدة لكل طلبية. والطلبية الطويلة تنقسم ورقتين.</t>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>ورقة وحدة لكل ورشة، من أول بند لآخر بند. اسم الورشة بيتكتب مرة وحدة فوق وبس.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>أدخل البنود بند بند. وكل بند بتدخله — اشطبه بالقلم على الورقة الأصلية. أي بند بضل بدون شطب = بند نسيته. هاي أهم خطوة بكل النموذج.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>التاريخ إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه. وإلا اتركه فاضي.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>المستلم: اكتب اسم اللي استلم البضاعة على كل بند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
           <t>المدقِّق — عمر المصري أو أبو علي</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>التدقيق من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «المدقق» لهذا البند.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>ابعث الملف + صورة الورقة الأصلية للأستاذ.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>الفكرة باختصار</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>وقت الطباعة: حدّد المدى المعبّى فقط، لأنه الورقة فيها 200 سطر فاضي جاهزين للورشة كلها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية لا مقابل الشاشة، ومعه شطب بالقلم على الورقة وقت الإدخال.</t>
         </is>
@@ -1308,9 +3344,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/نموذج_طلبية_ورشة.xlsx
+++ b/نموذج_طلبية_ورشة.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'الورشة'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'الورشة'!$A$1:$G$208</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -227,7 +227,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -265,6 +265,19 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00F0F8F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="009A4A00"/>
+        <sz val="11"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00FFE0C2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3158,6 +3171,9 @@
     <cfRule type="expression" priority="5" dxfId="3">
       <formula>$G7&lt;&gt;""</formula>
     </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4">
+      <formula>AND(ISNUMBER($C7),$C7&lt;0)</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="G7:G206" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3175,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3259,11 +3275,11 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>المدقِّق — عمر المصري أو أبو علي</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>المرتجع</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
           <t>6</t>
@@ -3271,11 +3287,11 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>التدقيق من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
+          <t>البضاعة الراجعة تنكتب سطر عادي بنفس الورقة، بتاريخ اليوم اللي رجعت فيه، والكمية بالسالب: «‎-5». السطر بيتلوّن برتقالي لحاله عشان ما ينقرأ غلط.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>7</t>
@@ -3283,7 +3299,7 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «المدقق» لهذا البند.</t>
+          <t>الإفرادي بسطر المرتجع = السعر اللي انباعت فيه، مش سعر الكتالوج. وإذا الراجع مكسور أو مفتوح وبدك تخصم عليه، اكتب سعر أقل — هاد اللي رح يترجع للمقاول.</t>
         </is>
       </c>
     </row>
@@ -3295,26 +3311,26 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+          <t>المستلم بسطر المرتجع = اللي رجّع البضاعة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>المدقِّق — عمر المصري أو أبو علي</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>ابعث الملف + صورة الورقة الأصلية للأستاذ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>الفكرة باختصار</t>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>التدقيق من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها.</t>
         </is>
       </c>
     </row>
@@ -3326,28 +3342,72 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
+          <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «المدقق» لهذا البند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>ابعث الملف + صورة الورقة الأصلية للأستاذ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
           <t>وقت الطباعة: حدّد المدى المعبّى فقط، لأنه الورقة فيها 200 سطر فاضي جاهزين للورشة كلها.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>الفكرة باختصار</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية لا مقابل الشاشة، ومعه شطب بالقلم على الورقة وقت الإدخال.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/نموذج_طلبية_ورشة.xlsx
+++ b/نموذج_طلبية_ورشة.xlsx
@@ -8,12 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="الورشة" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="التعليمات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="المرتجعات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="التعليمات" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'الورشة'!$1:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'الورشة'!$A$1:$G$208</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'التعليمات'!$A$1:$B$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'المرتجعات'!$1:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'المرتجعات'!$A$1:$G$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'التعليمات'!$A$1:$B$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -49,13 +52,13 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="11"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="13"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -93,7 +96,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +131,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F6E6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009A4A00"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -179,11 +187,12 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -214,6 +223,15 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -223,11 +241,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -265,19 +286,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00F0F8F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="009A4A00"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="00FFE0C2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -669,6 +677,11 @@
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
     </row>
     <row r="3"/>
     <row r="4" ht="26" customHeight="1">
@@ -677,7 +690,7 @@
           <t>البنود المُدخلة</t>
         </is>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="5">
         <f>COUNTA(B7:B206)</f>
         <v/>
       </c>
@@ -686,2456 +699,2456 @@
           <t>المدقَّقة</t>
         </is>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <f>COUNTA(G7:G206)</f>
         <v/>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="6">
         <f>IF(B4=0,"⛔ ما في بنود مُدخلة",IF(D4&lt;B4,"⛔ باقي "&amp;(B4-D4)&amp;" بند بدون تدقيق","✅ كل البنود مدقَّقة"))</f>
         <v/>
       </c>
     </row>
     <row r="5"/>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>البند</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>الكمية</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>الإفرادي</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>المستلم</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>المدقق</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <f>IF(B7="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
     </row>
     <row r="8" ht="21" customHeight="1">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <f>IF(B8="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="7">
+      <c r="A9" s="8">
         <f>IF(B9="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
     </row>
     <row r="10" ht="21" customHeight="1">
-      <c r="A10" s="7">
+      <c r="A10" s="8">
         <f>IF(B10="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="7">
+      <c r="A11" s="8">
         <f>IF(B11="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1">
-      <c r="A12" s="7">
+      <c r="A12" s="8">
         <f>IF(B12="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <f>IF(B13="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="7">
+      <c r="A14" s="8">
         <f>IF(B14="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="7">
+      <c r="A15" s="8">
         <f>IF(B15="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
     </row>
     <row r="16" ht="21" customHeight="1">
-      <c r="A16" s="7">
+      <c r="A16" s="8">
         <f>IF(B16="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <f>IF(B17="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
     </row>
     <row r="18" ht="21" customHeight="1">
-      <c r="A18" s="7">
+      <c r="A18" s="8">
         <f>IF(B18="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="7">
+      <c r="A19" s="8">
         <f>IF(B19="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="7">
+      <c r="A20" s="8">
         <f>IF(B20="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="7">
+      <c r="A21" s="8">
         <f>IF(B21="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="7">
+      <c r="A22" s="8">
         <f>IF(B22="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="7">
+      <c r="A23" s="8">
         <f>IF(B23="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="7">
+      <c r="A24" s="8">
         <f>IF(B24="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="7">
+      <c r="A25" s="8">
         <f>IF(B25="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="7">
+      <c r="A26" s="8">
         <f>IF(B26="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="10" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="7">
+      <c r="A27" s="8">
         <f>IF(B27="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="7">
+      <c r="A28" s="8">
         <f>IF(B28="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="7">
+      <c r="A29" s="8">
         <f>IF(B29="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="7">
+      <c r="A30" s="8">
         <f>IF(B30="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="7">
+      <c r="A31" s="8">
         <f>IF(B31="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="7">
+      <c r="A32" s="8">
         <f>IF(B32="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="7">
+      <c r="A33" s="8">
         <f>IF(B33="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1">
-      <c r="A34" s="7">
+      <c r="A34" s="8">
         <f>IF(B34="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1">
-      <c r="A35" s="7">
+      <c r="A35" s="8">
         <f>IF(B35="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
     </row>
     <row r="36" ht="21" customHeight="1">
-      <c r="A36" s="7">
+      <c r="A36" s="8">
         <f>IF(B36="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="9" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
-      <c r="A37" s="7">
+      <c r="A37" s="8">
         <f>IF(B37="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
-      <c r="A38" s="7">
+      <c r="A38" s="8">
         <f>IF(B38="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="A39" s="7">
+      <c r="A39" s="8">
         <f>IF(B39="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
     </row>
     <row r="40" ht="21" customHeight="1">
-      <c r="A40" s="7">
+      <c r="A40" s="8">
         <f>IF(B40="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
     </row>
     <row r="41" ht="21" customHeight="1">
-      <c r="A41" s="7">
+      <c r="A41" s="8">
         <f>IF(B41="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="9" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
     </row>
     <row r="42" ht="21" customHeight="1">
-      <c r="A42" s="7">
+      <c r="A42" s="8">
         <f>IF(B42="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="9" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1">
-      <c r="A43" s="7">
+      <c r="A43" s="8">
         <f>IF(B43="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
     </row>
     <row r="44" ht="21" customHeight="1">
-      <c r="A44" s="7">
+      <c r="A44" s="8">
         <f>IF(B44="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="A45" s="7">
+      <c r="A45" s="8">
         <f>IF(B45="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="9" t="n"/>
-      <c r="G45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
     </row>
     <row r="46" ht="21" customHeight="1">
-      <c r="A46" s="7">
+      <c r="A46" s="8">
         <f>IF(B46="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="9" t="n"/>
-      <c r="G46" s="9" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
     </row>
     <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="7">
+      <c r="A47" s="8">
         <f>IF(B47="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="10" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="9" t="n"/>
-      <c r="G47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
     </row>
     <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="7">
+      <c r="A48" s="8">
         <f>IF(B48="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="9" t="n"/>
-      <c r="D48" s="10" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="9" t="n"/>
-      <c r="G48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
     </row>
     <row r="49" ht="21" customHeight="1">
-      <c r="A49" s="7">
+      <c r="A49" s="8">
         <f>IF(B49="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="9" t="n"/>
-      <c r="G49" s="9" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
     </row>
     <row r="50" ht="21" customHeight="1">
-      <c r="A50" s="7">
+      <c r="A50" s="8">
         <f>IF(B50="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="10" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="9" t="n"/>
-      <c r="G50" s="9" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
     </row>
     <row r="51" ht="21" customHeight="1">
-      <c r="A51" s="7">
+      <c r="A51" s="8">
         <f>IF(B51="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="10" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="9" t="n"/>
-      <c r="G51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="A52" s="7">
+      <c r="A52" s="8">
         <f>IF(B52="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="9" t="n"/>
-      <c r="G52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
     </row>
     <row r="53" ht="21" customHeight="1">
-      <c r="A53" s="7">
+      <c r="A53" s="8">
         <f>IF(B53="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="10" t="n"/>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="9" t="n"/>
-      <c r="G53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
     </row>
     <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="7">
+      <c r="A54" s="8">
         <f>IF(B54="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="9" t="n"/>
-      <c r="D54" s="10" t="n"/>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="9" t="n"/>
-      <c r="G54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1">
-      <c r="A55" s="7">
+      <c r="A55" s="8">
         <f>IF(B55="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="9" t="n"/>
-      <c r="D55" s="10" t="n"/>
-      <c r="E55" s="11" t="n"/>
-      <c r="F55" s="9" t="n"/>
-      <c r="G55" s="9" t="n"/>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
     </row>
     <row r="56" ht="21" customHeight="1">
-      <c r="A56" s="7">
+      <c r="A56" s="8">
         <f>IF(B56="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="10" t="n"/>
-      <c r="E56" s="11" t="n"/>
-      <c r="F56" s="9" t="n"/>
-      <c r="G56" s="9" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
     </row>
     <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="7">
+      <c r="A57" s="8">
         <f>IF(B57="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="9" t="n"/>
-      <c r="D57" s="10" t="n"/>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="9" t="n"/>
-      <c r="G57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
     </row>
     <row r="58" ht="21" customHeight="1">
-      <c r="A58" s="7">
+      <c r="A58" s="8">
         <f>IF(B58="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="9" t="n"/>
-      <c r="D58" s="10" t="n"/>
-      <c r="E58" s="11" t="n"/>
-      <c r="F58" s="9" t="n"/>
-      <c r="G58" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
     </row>
     <row r="59" ht="21" customHeight="1">
-      <c r="A59" s="7">
+      <c r="A59" s="8">
         <f>IF(B59="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="9" t="n"/>
-      <c r="D59" s="10" t="n"/>
-      <c r="E59" s="11" t="n"/>
-      <c r="F59" s="9" t="n"/>
-      <c r="G59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
     </row>
     <row r="60" ht="21" customHeight="1">
-      <c r="A60" s="7">
+      <c r="A60" s="8">
         <f>IF(B60="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="9" t="n"/>
-      <c r="D60" s="10" t="n"/>
-      <c r="E60" s="11" t="n"/>
-      <c r="F60" s="9" t="n"/>
-      <c r="G60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
     </row>
     <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="7">
+      <c r="A61" s="8">
         <f>IF(B61="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="9" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="9" t="n"/>
-      <c r="G61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
     </row>
     <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="7">
+      <c r="A62" s="8">
         <f>IF(B62="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="9" t="n"/>
-      <c r="D62" s="10" t="n"/>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="9" t="n"/>
-      <c r="G62" s="9" t="n"/>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="A63" s="7">
+      <c r="A63" s="8">
         <f>IF(B63="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="9" t="n"/>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="11" t="n"/>
-      <c r="F63" s="9" t="n"/>
-      <c r="G63" s="9" t="n"/>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="A64" s="7">
+      <c r="A64" s="8">
         <f>IF(B64="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="9" t="n"/>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="11" t="n"/>
-      <c r="F64" s="9" t="n"/>
-      <c r="G64" s="9" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="7">
+      <c r="A65" s="8">
         <f>IF(B65="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="9" t="n"/>
-      <c r="D65" s="10" t="n"/>
-      <c r="E65" s="11" t="n"/>
-      <c r="F65" s="9" t="n"/>
-      <c r="G65" s="9" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
     </row>
     <row r="66" ht="21" customHeight="1">
-      <c r="A66" s="7">
+      <c r="A66" s="8">
         <f>IF(B66="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="9" t="n"/>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="11" t="n"/>
-      <c r="F66" s="9" t="n"/>
-      <c r="G66" s="9" t="n"/>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="7">
+      <c r="A67" s="8">
         <f>IF(B67="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="11" t="n"/>
-      <c r="F67" s="9" t="n"/>
-      <c r="G67" s="9" t="n"/>
+      <c r="B67" s="9" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
     </row>
     <row r="68" ht="21" customHeight="1">
-      <c r="A68" s="7">
+      <c r="A68" s="8">
         <f>IF(B68="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="9" t="n"/>
-      <c r="D68" s="10" t="n"/>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="9" t="n"/>
-      <c r="G68" s="9" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
     </row>
     <row r="69" ht="21" customHeight="1">
-      <c r="A69" s="7">
+      <c r="A69" s="8">
         <f>IF(B69="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="9" t="n"/>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="11" t="n"/>
-      <c r="F69" s="9" t="n"/>
-      <c r="G69" s="9" t="n"/>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
     </row>
     <row r="70" ht="21" customHeight="1">
-      <c r="A70" s="7">
+      <c r="A70" s="8">
         <f>IF(B70="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="9" t="n"/>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="9" t="n"/>
-      <c r="G70" s="9" t="n"/>
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
     </row>
     <row r="71" ht="21" customHeight="1">
-      <c r="A71" s="7">
+      <c r="A71" s="8">
         <f>IF(B71="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="9" t="n"/>
-      <c r="D71" s="10" t="n"/>
-      <c r="E71" s="11" t="n"/>
-      <c r="F71" s="9" t="n"/>
-      <c r="G71" s="9" t="n"/>
+      <c r="B71" s="9" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="11" t="n"/>
+      <c r="E71" s="12" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
     </row>
     <row r="72" ht="21" customHeight="1">
-      <c r="A72" s="7">
+      <c r="A72" s="8">
         <f>IF(B72="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="9" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="9" t="n"/>
-      <c r="G72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
     </row>
     <row r="73" ht="21" customHeight="1">
-      <c r="A73" s="7">
+      <c r="A73" s="8">
         <f>IF(B73="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="9" t="n"/>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="11" t="n"/>
-      <c r="F73" s="9" t="n"/>
-      <c r="G73" s="9" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="11" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
     </row>
     <row r="74" ht="21" customHeight="1">
-      <c r="A74" s="7">
+      <c r="A74" s="8">
         <f>IF(B74="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B74" s="8" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="10" t="n"/>
-      <c r="E74" s="11" t="n"/>
-      <c r="F74" s="9" t="n"/>
-      <c r="G74" s="9" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
     </row>
     <row r="75" ht="21" customHeight="1">
-      <c r="A75" s="7">
+      <c r="A75" s="8">
         <f>IF(B75="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="9" t="n"/>
-      <c r="D75" s="10" t="n"/>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="9" t="n"/>
-      <c r="G75" s="9" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="11" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
     </row>
     <row r="76" ht="21" customHeight="1">
-      <c r="A76" s="7">
+      <c r="A76" s="8">
         <f>IF(B76="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="9" t="n"/>
-      <c r="D76" s="10" t="n"/>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="9" t="n"/>
-      <c r="G76" s="9" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="11" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
     </row>
     <row r="77" ht="21" customHeight="1">
-      <c r="A77" s="7">
+      <c r="A77" s="8">
         <f>IF(B77="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="9" t="n"/>
-      <c r="D77" s="10" t="n"/>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="9" t="n"/>
-      <c r="G77" s="9" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
     </row>
     <row r="78" ht="21" customHeight="1">
-      <c r="A78" s="7">
+      <c r="A78" s="8">
         <f>IF(B78="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="9" t="n"/>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="11" t="n"/>
-      <c r="F78" s="9" t="n"/>
-      <c r="G78" s="9" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
     </row>
     <row r="79" ht="21" customHeight="1">
-      <c r="A79" s="7">
+      <c r="A79" s="8">
         <f>IF(B79="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B79" s="8" t="n"/>
-      <c r="C79" s="9" t="n"/>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="11" t="n"/>
-      <c r="F79" s="9" t="n"/>
-      <c r="G79" s="9" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
     </row>
     <row r="80" ht="21" customHeight="1">
-      <c r="A80" s="7">
+      <c r="A80" s="8">
         <f>IF(B80="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="9" t="n"/>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="11" t="n"/>
-      <c r="F80" s="9" t="n"/>
-      <c r="G80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="10" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
     </row>
     <row r="81" ht="21" customHeight="1">
-      <c r="A81" s="7">
+      <c r="A81" s="8">
         <f>IF(B81="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="9" t="n"/>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="11" t="n"/>
-      <c r="F81" s="9" t="n"/>
-      <c r="G81" s="9" t="n"/>
+      <c r="B81" s="9" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
     </row>
     <row r="82" ht="21" customHeight="1">
-      <c r="A82" s="7">
+      <c r="A82" s="8">
         <f>IF(B82="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="9" t="n"/>
-      <c r="D82" s="10" t="n"/>
-      <c r="E82" s="11" t="n"/>
-      <c r="F82" s="9" t="n"/>
-      <c r="G82" s="9" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
     </row>
     <row r="83" ht="21" customHeight="1">
-      <c r="A83" s="7">
+      <c r="A83" s="8">
         <f>IF(B83="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="9" t="n"/>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="11" t="n"/>
-      <c r="F83" s="9" t="n"/>
-      <c r="G83" s="9" t="n"/>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="11" t="n"/>
+      <c r="E83" s="12" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
     </row>
     <row r="84" ht="21" customHeight="1">
-      <c r="A84" s="7">
+      <c r="A84" s="8">
         <f>IF(B84="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="9" t="n"/>
-      <c r="D84" s="10" t="n"/>
-      <c r="E84" s="11" t="n"/>
-      <c r="F84" s="9" t="n"/>
-      <c r="G84" s="9" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
     </row>
     <row r="85" ht="21" customHeight="1">
-      <c r="A85" s="7">
+      <c r="A85" s="8">
         <f>IF(B85="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="11" t="n"/>
-      <c r="F85" s="9" t="n"/>
-      <c r="G85" s="9" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="12" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
     </row>
     <row r="86" ht="21" customHeight="1">
-      <c r="A86" s="7">
+      <c r="A86" s="8">
         <f>IF(B86="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="10" t="n"/>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="9" t="n"/>
-      <c r="G86" s="9" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="11" t="n"/>
+      <c r="E86" s="12" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
     </row>
     <row r="87" ht="21" customHeight="1">
-      <c r="A87" s="7">
+      <c r="A87" s="8">
         <f>IF(B87="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B87" s="8" t="n"/>
-      <c r="C87" s="9" t="n"/>
-      <c r="D87" s="10" t="n"/>
-      <c r="E87" s="11" t="n"/>
-      <c r="F87" s="9" t="n"/>
-      <c r="G87" s="9" t="n"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="12" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
     </row>
     <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="7">
+      <c r="A88" s="8">
         <f>IF(B88="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="10" t="n"/>
-      <c r="E88" s="11" t="n"/>
-      <c r="F88" s="9" t="n"/>
-      <c r="G88" s="9" t="n"/>
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="11" t="n"/>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
     </row>
     <row r="89" ht="21" customHeight="1">
-      <c r="A89" s="7">
+      <c r="A89" s="8">
         <f>IF(B89="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B89" s="8" t="n"/>
-      <c r="C89" s="9" t="n"/>
-      <c r="D89" s="10" t="n"/>
-      <c r="E89" s="11" t="n"/>
-      <c r="F89" s="9" t="n"/>
-      <c r="G89" s="9" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="10" t="n"/>
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="12" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
     </row>
     <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="7">
+      <c r="A90" s="8">
         <f>IF(B90="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="11" t="n"/>
-      <c r="F90" s="9" t="n"/>
-      <c r="G90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="11" t="n"/>
+      <c r="E90" s="12" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
     </row>
     <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="7">
+      <c r="A91" s="8">
         <f>IF(B91="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="11" t="n"/>
-      <c r="F91" s="9" t="n"/>
-      <c r="G91" s="9" t="n"/>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="10" t="n"/>
+      <c r="D91" s="11" t="n"/>
+      <c r="E91" s="12" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
     </row>
     <row r="92" ht="21" customHeight="1">
-      <c r="A92" s="7">
+      <c r="A92" s="8">
         <f>IF(B92="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B92" s="8" t="n"/>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="10" t="n"/>
-      <c r="E92" s="11" t="n"/>
-      <c r="F92" s="9" t="n"/>
-      <c r="G92" s="9" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
     </row>
     <row r="93" ht="21" customHeight="1">
-      <c r="A93" s="7">
+      <c r="A93" s="8">
         <f>IF(B93="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B93" s="8" t="n"/>
-      <c r="C93" s="9" t="n"/>
-      <c r="D93" s="10" t="n"/>
-      <c r="E93" s="11" t="n"/>
-      <c r="F93" s="9" t="n"/>
-      <c r="G93" s="9" t="n"/>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="10" t="n"/>
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="12" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
     </row>
     <row r="94" ht="21" customHeight="1">
-      <c r="A94" s="7">
+      <c r="A94" s="8">
         <f>IF(B94="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="9" t="n"/>
-      <c r="D94" s="10" t="n"/>
-      <c r="E94" s="11" t="n"/>
-      <c r="F94" s="9" t="n"/>
-      <c r="G94" s="9" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
     </row>
     <row r="95" ht="21" customHeight="1">
-      <c r="A95" s="7">
+      <c r="A95" s="8">
         <f>IF(B95="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B95" s="8" t="n"/>
-      <c r="C95" s="9" t="n"/>
-      <c r="D95" s="10" t="n"/>
-      <c r="E95" s="11" t="n"/>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="9" t="n"/>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="11" t="n"/>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
     </row>
     <row r="96" ht="21" customHeight="1">
-      <c r="A96" s="7">
+      <c r="A96" s="8">
         <f>IF(B96="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="9" t="n"/>
-      <c r="D96" s="10" t="n"/>
-      <c r="E96" s="11" t="n"/>
-      <c r="F96" s="9" t="n"/>
-      <c r="G96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" s="7">
+      <c r="A97" s="8">
         <f>IF(B97="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B97" s="8" t="n"/>
-      <c r="C97" s="9" t="n"/>
-      <c r="D97" s="10" t="n"/>
-      <c r="E97" s="11" t="n"/>
-      <c r="F97" s="9" t="n"/>
-      <c r="G97" s="9" t="n"/>
+      <c r="B97" s="9" t="n"/>
+      <c r="C97" s="10" t="n"/>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="12" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
     </row>
     <row r="98" ht="21" customHeight="1">
-      <c r="A98" s="7">
+      <c r="A98" s="8">
         <f>IF(B98="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="9" t="n"/>
-      <c r="D98" s="10" t="n"/>
-      <c r="E98" s="11" t="n"/>
-      <c r="F98" s="9" t="n"/>
-      <c r="G98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="10" t="n"/>
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
     </row>
     <row r="99" ht="21" customHeight="1">
-      <c r="A99" s="7">
+      <c r="A99" s="8">
         <f>IF(B99="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B99" s="8" t="n"/>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="10" t="n"/>
-      <c r="E99" s="11" t="n"/>
-      <c r="F99" s="9" t="n"/>
-      <c r="G99" s="9" t="n"/>
+      <c r="B99" s="9" t="n"/>
+      <c r="C99" s="10" t="n"/>
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="12" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
     </row>
     <row r="100" ht="21" customHeight="1">
-      <c r="A100" s="7">
+      <c r="A100" s="8">
         <f>IF(B100="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="9" t="n"/>
-      <c r="D100" s="10" t="n"/>
-      <c r="E100" s="11" t="n"/>
-      <c r="F100" s="9" t="n"/>
-      <c r="G100" s="9" t="n"/>
+      <c r="B100" s="9" t="n"/>
+      <c r="C100" s="10" t="n"/>
+      <c r="D100" s="11" t="n"/>
+      <c r="E100" s="12" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
     </row>
     <row r="101" ht="21" customHeight="1">
-      <c r="A101" s="7">
+      <c r="A101" s="8">
         <f>IF(B101="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="9" t="n"/>
-      <c r="D101" s="10" t="n"/>
-      <c r="E101" s="11" t="n"/>
-      <c r="F101" s="9" t="n"/>
-      <c r="G101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="10" t="n"/>
+      <c r="D101" s="11" t="n"/>
+      <c r="E101" s="12" t="n"/>
+      <c r="F101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
     </row>
     <row r="102" ht="21" customHeight="1">
-      <c r="A102" s="7">
+      <c r="A102" s="8">
         <f>IF(B102="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="9" t="n"/>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="11" t="n"/>
-      <c r="F102" s="9" t="n"/>
-      <c r="G102" s="9" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="10" t="n"/>
+      <c r="D102" s="11" t="n"/>
+      <c r="E102" s="12" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
     </row>
     <row r="103" ht="21" customHeight="1">
-      <c r="A103" s="7">
+      <c r="A103" s="8">
         <f>IF(B103="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="9" t="n"/>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="11" t="n"/>
-      <c r="F103" s="9" t="n"/>
-      <c r="G103" s="9" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="11" t="n"/>
+      <c r="E103" s="12" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
     </row>
     <row r="104" ht="21" customHeight="1">
-      <c r="A104" s="7">
+      <c r="A104" s="8">
         <f>IF(B104="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B104" s="8" t="n"/>
-      <c r="C104" s="9" t="n"/>
-      <c r="D104" s="10" t="n"/>
-      <c r="E104" s="11" t="n"/>
-      <c r="F104" s="9" t="n"/>
-      <c r="G104" s="9" t="n"/>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="10" t="n"/>
+      <c r="D104" s="11" t="n"/>
+      <c r="E104" s="12" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
     </row>
     <row r="105" ht="21" customHeight="1">
-      <c r="A105" s="7">
+      <c r="A105" s="8">
         <f>IF(B105="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="9" t="n"/>
-      <c r="D105" s="10" t="n"/>
-      <c r="E105" s="11" t="n"/>
-      <c r="F105" s="9" t="n"/>
-      <c r="G105" s="9" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="10" t="n"/>
+      <c r="D105" s="11" t="n"/>
+      <c r="E105" s="12" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
     </row>
     <row r="106" ht="21" customHeight="1">
-      <c r="A106" s="7">
+      <c r="A106" s="8">
         <f>IF(B106="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="9" t="n"/>
-      <c r="D106" s="10" t="n"/>
-      <c r="E106" s="11" t="n"/>
-      <c r="F106" s="9" t="n"/>
-      <c r="G106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="10" t="n"/>
+      <c r="D106" s="11" t="n"/>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
     </row>
     <row r="107" ht="21" customHeight="1">
-      <c r="A107" s="7">
+      <c r="A107" s="8">
         <f>IF(B107="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="9" t="n"/>
-      <c r="D107" s="10" t="n"/>
-      <c r="E107" s="11" t="n"/>
-      <c r="F107" s="9" t="n"/>
-      <c r="G107" s="9" t="n"/>
+      <c r="B107" s="9" t="n"/>
+      <c r="C107" s="10" t="n"/>
+      <c r="D107" s="11" t="n"/>
+      <c r="E107" s="12" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
     </row>
     <row r="108" ht="21" customHeight="1">
-      <c r="A108" s="7">
+      <c r="A108" s="8">
         <f>IF(B108="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="9" t="n"/>
-      <c r="D108" s="10" t="n"/>
-      <c r="E108" s="11" t="n"/>
-      <c r="F108" s="9" t="n"/>
-      <c r="G108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="10" t="n"/>
+      <c r="D108" s="11" t="n"/>
+      <c r="E108" s="12" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
     </row>
     <row r="109" ht="21" customHeight="1">
-      <c r="A109" s="7">
+      <c r="A109" s="8">
         <f>IF(B109="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="9" t="n"/>
-      <c r="D109" s="10" t="n"/>
-      <c r="E109" s="11" t="n"/>
-      <c r="F109" s="9" t="n"/>
-      <c r="G109" s="9" t="n"/>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="11" t="n"/>
+      <c r="E109" s="12" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
     </row>
     <row r="110" ht="21" customHeight="1">
-      <c r="A110" s="7">
+      <c r="A110" s="8">
         <f>IF(B110="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="9" t="n"/>
-      <c r="D110" s="10" t="n"/>
-      <c r="E110" s="11" t="n"/>
-      <c r="F110" s="9" t="n"/>
-      <c r="G110" s="9" t="n"/>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="10" t="n"/>
+      <c r="D110" s="11" t="n"/>
+      <c r="E110" s="12" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
     </row>
     <row r="111" ht="21" customHeight="1">
-      <c r="A111" s="7">
+      <c r="A111" s="8">
         <f>IF(B111="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="9" t="n"/>
-      <c r="D111" s="10" t="n"/>
-      <c r="E111" s="11" t="n"/>
-      <c r="F111" s="9" t="n"/>
-      <c r="G111" s="9" t="n"/>
+      <c r="B111" s="9" t="n"/>
+      <c r="C111" s="10" t="n"/>
+      <c r="D111" s="11" t="n"/>
+      <c r="E111" s="12" t="n"/>
+      <c r="F111" s="10" t="n"/>
+      <c r="G111" s="10" t="n"/>
     </row>
     <row r="112" ht="21" customHeight="1">
-      <c r="A112" s="7">
+      <c r="A112" s="8">
         <f>IF(B112="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="9" t="n"/>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="11" t="n"/>
-      <c r="F112" s="9" t="n"/>
-      <c r="G112" s="9" t="n"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="10" t="n"/>
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="12" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
     </row>
     <row r="113" ht="21" customHeight="1">
-      <c r="A113" s="7">
+      <c r="A113" s="8">
         <f>IF(B113="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="9" t="n"/>
-      <c r="D113" s="10" t="n"/>
-      <c r="E113" s="11" t="n"/>
-      <c r="F113" s="9" t="n"/>
-      <c r="G113" s="9" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="11" t="n"/>
+      <c r="E113" s="12" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
     </row>
     <row r="114" ht="21" customHeight="1">
-      <c r="A114" s="7">
+      <c r="A114" s="8">
         <f>IF(B114="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="9" t="n"/>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="11" t="n"/>
-      <c r="F114" s="9" t="n"/>
-      <c r="G114" s="9" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="11" t="n"/>
+      <c r="E114" s="12" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
     </row>
     <row r="115" ht="21" customHeight="1">
-      <c r="A115" s="7">
+      <c r="A115" s="8">
         <f>IF(B115="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="9" t="n"/>
-      <c r="D115" s="10" t="n"/>
-      <c r="E115" s="11" t="n"/>
-      <c r="F115" s="9" t="n"/>
-      <c r="G115" s="9" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="10" t="n"/>
+      <c r="D115" s="11" t="n"/>
+      <c r="E115" s="12" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
     </row>
     <row r="116" ht="21" customHeight="1">
-      <c r="A116" s="7">
+      <c r="A116" s="8">
         <f>IF(B116="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B116" s="8" t="n"/>
-      <c r="C116" s="9" t="n"/>
-      <c r="D116" s="10" t="n"/>
-      <c r="E116" s="11" t="n"/>
-      <c r="F116" s="9" t="n"/>
-      <c r="G116" s="9" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="11" t="n"/>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
     </row>
     <row r="117" ht="21" customHeight="1">
-      <c r="A117" s="7">
+      <c r="A117" s="8">
         <f>IF(B117="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B117" s="8" t="n"/>
-      <c r="C117" s="9" t="n"/>
-      <c r="D117" s="10" t="n"/>
-      <c r="E117" s="11" t="n"/>
-      <c r="F117" s="9" t="n"/>
-      <c r="G117" s="9" t="n"/>
+      <c r="B117" s="9" t="n"/>
+      <c r="C117" s="10" t="n"/>
+      <c r="D117" s="11" t="n"/>
+      <c r="E117" s="12" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
     </row>
     <row r="118" ht="21" customHeight="1">
-      <c r="A118" s="7">
+      <c r="A118" s="8">
         <f>IF(B118="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B118" s="8" t="n"/>
-      <c r="C118" s="9" t="n"/>
-      <c r="D118" s="10" t="n"/>
-      <c r="E118" s="11" t="n"/>
-      <c r="F118" s="9" t="n"/>
-      <c r="G118" s="9" t="n"/>
+      <c r="B118" s="9" t="n"/>
+      <c r="C118" s="10" t="n"/>
+      <c r="D118" s="11" t="n"/>
+      <c r="E118" s="12" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
     </row>
     <row r="119" ht="21" customHeight="1">
-      <c r="A119" s="7">
+      <c r="A119" s="8">
         <f>IF(B119="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="9" t="n"/>
-      <c r="D119" s="10" t="n"/>
-      <c r="E119" s="11" t="n"/>
-      <c r="F119" s="9" t="n"/>
-      <c r="G119" s="9" t="n"/>
+      <c r="B119" s="9" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="11" t="n"/>
+      <c r="E119" s="12" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
     </row>
     <row r="120" ht="21" customHeight="1">
-      <c r="A120" s="7">
+      <c r="A120" s="8">
         <f>IF(B120="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="9" t="n"/>
-      <c r="D120" s="10" t="n"/>
-      <c r="E120" s="11" t="n"/>
-      <c r="F120" s="9" t="n"/>
-      <c r="G120" s="9" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="10" t="n"/>
+      <c r="D120" s="11" t="n"/>
+      <c r="E120" s="12" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
     </row>
     <row r="121" ht="21" customHeight="1">
-      <c r="A121" s="7">
+      <c r="A121" s="8">
         <f>IF(B121="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B121" s="8" t="n"/>
-      <c r="C121" s="9" t="n"/>
-      <c r="D121" s="10" t="n"/>
-      <c r="E121" s="11" t="n"/>
-      <c r="F121" s="9" t="n"/>
-      <c r="G121" s="9" t="n"/>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="10" t="n"/>
+      <c r="D121" s="11" t="n"/>
+      <c r="E121" s="12" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
     </row>
     <row r="122" ht="21" customHeight="1">
-      <c r="A122" s="7">
+      <c r="A122" s="8">
         <f>IF(B122="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B122" s="8" t="n"/>
-      <c r="C122" s="9" t="n"/>
-      <c r="D122" s="10" t="n"/>
-      <c r="E122" s="11" t="n"/>
-      <c r="F122" s="9" t="n"/>
-      <c r="G122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="10" t="n"/>
+      <c r="D122" s="11" t="n"/>
+      <c r="E122" s="12" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
     </row>
     <row r="123" ht="21" customHeight="1">
-      <c r="A123" s="7">
+      <c r="A123" s="8">
         <f>IF(B123="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B123" s="8" t="n"/>
-      <c r="C123" s="9" t="n"/>
-      <c r="D123" s="10" t="n"/>
-      <c r="E123" s="11" t="n"/>
-      <c r="F123" s="9" t="n"/>
-      <c r="G123" s="9" t="n"/>
+      <c r="B123" s="9" t="n"/>
+      <c r="C123" s="10" t="n"/>
+      <c r="D123" s="11" t="n"/>
+      <c r="E123" s="12" t="n"/>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
     </row>
     <row r="124" ht="21" customHeight="1">
-      <c r="A124" s="7">
+      <c r="A124" s="8">
         <f>IF(B124="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B124" s="8" t="n"/>
-      <c r="C124" s="9" t="n"/>
-      <c r="D124" s="10" t="n"/>
-      <c r="E124" s="11" t="n"/>
-      <c r="F124" s="9" t="n"/>
-      <c r="G124" s="9" t="n"/>
+      <c r="B124" s="9" t="n"/>
+      <c r="C124" s="10" t="n"/>
+      <c r="D124" s="11" t="n"/>
+      <c r="E124" s="12" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
     </row>
     <row r="125" ht="21" customHeight="1">
-      <c r="A125" s="7">
+      <c r="A125" s="8">
         <f>IF(B125="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B125" s="8" t="n"/>
-      <c r="C125" s="9" t="n"/>
-      <c r="D125" s="10" t="n"/>
-      <c r="E125" s="11" t="n"/>
-      <c r="F125" s="9" t="n"/>
-      <c r="G125" s="9" t="n"/>
+      <c r="B125" s="9" t="n"/>
+      <c r="C125" s="10" t="n"/>
+      <c r="D125" s="11" t="n"/>
+      <c r="E125" s="12" t="n"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
     </row>
     <row r="126" ht="21" customHeight="1">
-      <c r="A126" s="7">
+      <c r="A126" s="8">
         <f>IF(B126="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B126" s="8" t="n"/>
-      <c r="C126" s="9" t="n"/>
-      <c r="D126" s="10" t="n"/>
-      <c r="E126" s="11" t="n"/>
-      <c r="F126" s="9" t="n"/>
-      <c r="G126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="10" t="n"/>
+      <c r="D126" s="11" t="n"/>
+      <c r="E126" s="12" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
     </row>
     <row r="127" ht="21" customHeight="1">
-      <c r="A127" s="7">
+      <c r="A127" s="8">
         <f>IF(B127="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B127" s="8" t="n"/>
-      <c r="C127" s="9" t="n"/>
-      <c r="D127" s="10" t="n"/>
-      <c r="E127" s="11" t="n"/>
-      <c r="F127" s="9" t="n"/>
-      <c r="G127" s="9" t="n"/>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="10" t="n"/>
+      <c r="D127" s="11" t="n"/>
+      <c r="E127" s="12" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
     </row>
     <row r="128" ht="21" customHeight="1">
-      <c r="A128" s="7">
+      <c r="A128" s="8">
         <f>IF(B128="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B128" s="8" t="n"/>
-      <c r="C128" s="9" t="n"/>
-      <c r="D128" s="10" t="n"/>
-      <c r="E128" s="11" t="n"/>
-      <c r="F128" s="9" t="n"/>
-      <c r="G128" s="9" t="n"/>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="10" t="n"/>
+      <c r="D128" s="11" t="n"/>
+      <c r="E128" s="12" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
     </row>
     <row r="129" ht="21" customHeight="1">
-      <c r="A129" s="7">
+      <c r="A129" s="8">
         <f>IF(B129="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B129" s="8" t="n"/>
-      <c r="C129" s="9" t="n"/>
-      <c r="D129" s="10" t="n"/>
-      <c r="E129" s="11" t="n"/>
-      <c r="F129" s="9" t="n"/>
-      <c r="G129" s="9" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="11" t="n"/>
+      <c r="E129" s="12" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
     </row>
     <row r="130" ht="21" customHeight="1">
-      <c r="A130" s="7">
+      <c r="A130" s="8">
         <f>IF(B130="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B130" s="8" t="n"/>
-      <c r="C130" s="9" t="n"/>
-      <c r="D130" s="10" t="n"/>
-      <c r="E130" s="11" t="n"/>
-      <c r="F130" s="9" t="n"/>
-      <c r="G130" s="9" t="n"/>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="10" t="n"/>
+      <c r="D130" s="11" t="n"/>
+      <c r="E130" s="12" t="n"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
     </row>
     <row r="131" ht="21" customHeight="1">
-      <c r="A131" s="7">
+      <c r="A131" s="8">
         <f>IF(B131="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B131" s="8" t="n"/>
-      <c r="C131" s="9" t="n"/>
-      <c r="D131" s="10" t="n"/>
-      <c r="E131" s="11" t="n"/>
-      <c r="F131" s="9" t="n"/>
-      <c r="G131" s="9" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="11" t="n"/>
+      <c r="E131" s="12" t="n"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
     </row>
     <row r="132" ht="21" customHeight="1">
-      <c r="A132" s="7">
+      <c r="A132" s="8">
         <f>IF(B132="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B132" s="8" t="n"/>
-      <c r="C132" s="9" t="n"/>
-      <c r="D132" s="10" t="n"/>
-      <c r="E132" s="11" t="n"/>
-      <c r="F132" s="9" t="n"/>
-      <c r="G132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="10" t="n"/>
+      <c r="D132" s="11" t="n"/>
+      <c r="E132" s="12" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
     </row>
     <row r="133" ht="21" customHeight="1">
-      <c r="A133" s="7">
+      <c r="A133" s="8">
         <f>IF(B133="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B133" s="8" t="n"/>
-      <c r="C133" s="9" t="n"/>
-      <c r="D133" s="10" t="n"/>
-      <c r="E133" s="11" t="n"/>
-      <c r="F133" s="9" t="n"/>
-      <c r="G133" s="9" t="n"/>
+      <c r="B133" s="9" t="n"/>
+      <c r="C133" s="10" t="n"/>
+      <c r="D133" s="11" t="n"/>
+      <c r="E133" s="12" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
     </row>
     <row r="134" ht="21" customHeight="1">
-      <c r="A134" s="7">
+      <c r="A134" s="8">
         <f>IF(B134="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B134" s="8" t="n"/>
-      <c r="C134" s="9" t="n"/>
-      <c r="D134" s="10" t="n"/>
-      <c r="E134" s="11" t="n"/>
-      <c r="F134" s="9" t="n"/>
-      <c r="G134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="10" t="n"/>
+      <c r="D134" s="11" t="n"/>
+      <c r="E134" s="12" t="n"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
     </row>
     <row r="135" ht="21" customHeight="1">
-      <c r="A135" s="7">
+      <c r="A135" s="8">
         <f>IF(B135="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B135" s="8" t="n"/>
-      <c r="C135" s="9" t="n"/>
-      <c r="D135" s="10" t="n"/>
-      <c r="E135" s="11" t="n"/>
-      <c r="F135" s="9" t="n"/>
-      <c r="G135" s="9" t="n"/>
+      <c r="B135" s="9" t="n"/>
+      <c r="C135" s="10" t="n"/>
+      <c r="D135" s="11" t="n"/>
+      <c r="E135" s="12" t="n"/>
+      <c r="F135" s="10" t="n"/>
+      <c r="G135" s="10" t="n"/>
     </row>
     <row r="136" ht="21" customHeight="1">
-      <c r="A136" s="7">
+      <c r="A136" s="8">
         <f>IF(B136="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B136" s="8" t="n"/>
-      <c r="C136" s="9" t="n"/>
-      <c r="D136" s="10" t="n"/>
-      <c r="E136" s="11" t="n"/>
-      <c r="F136" s="9" t="n"/>
-      <c r="G136" s="9" t="n"/>
+      <c r="B136" s="9" t="n"/>
+      <c r="C136" s="10" t="n"/>
+      <c r="D136" s="11" t="n"/>
+      <c r="E136" s="12" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
     </row>
     <row r="137" ht="21" customHeight="1">
-      <c r="A137" s="7">
+      <c r="A137" s="8">
         <f>IF(B137="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B137" s="8" t="n"/>
-      <c r="C137" s="9" t="n"/>
-      <c r="D137" s="10" t="n"/>
-      <c r="E137" s="11" t="n"/>
-      <c r="F137" s="9" t="n"/>
-      <c r="G137" s="9" t="n"/>
+      <c r="B137" s="9" t="n"/>
+      <c r="C137" s="10" t="n"/>
+      <c r="D137" s="11" t="n"/>
+      <c r="E137" s="12" t="n"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
     </row>
     <row r="138" ht="21" customHeight="1">
-      <c r="A138" s="7">
+      <c r="A138" s="8">
         <f>IF(B138="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B138" s="8" t="n"/>
-      <c r="C138" s="9" t="n"/>
-      <c r="D138" s="10" t="n"/>
-      <c r="E138" s="11" t="n"/>
-      <c r="F138" s="9" t="n"/>
-      <c r="G138" s="9" t="n"/>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="10" t="n"/>
+      <c r="D138" s="11" t="n"/>
+      <c r="E138" s="12" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
     </row>
     <row r="139" ht="21" customHeight="1">
-      <c r="A139" s="7">
+      <c r="A139" s="8">
         <f>IF(B139="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B139" s="8" t="n"/>
-      <c r="C139" s="9" t="n"/>
-      <c r="D139" s="10" t="n"/>
-      <c r="E139" s="11" t="n"/>
-      <c r="F139" s="9" t="n"/>
-      <c r="G139" s="9" t="n"/>
+      <c r="B139" s="9" t="n"/>
+      <c r="C139" s="10" t="n"/>
+      <c r="D139" s="11" t="n"/>
+      <c r="E139" s="12" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
     </row>
     <row r="140" ht="21" customHeight="1">
-      <c r="A140" s="7">
+      <c r="A140" s="8">
         <f>IF(B140="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B140" s="8" t="n"/>
-      <c r="C140" s="9" t="n"/>
-      <c r="D140" s="10" t="n"/>
-      <c r="E140" s="11" t="n"/>
-      <c r="F140" s="9" t="n"/>
-      <c r="G140" s="9" t="n"/>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="11" t="n"/>
+      <c r="E140" s="12" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
     </row>
     <row r="141" ht="21" customHeight="1">
-      <c r="A141" s="7">
+      <c r="A141" s="8">
         <f>IF(B141="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B141" s="8" t="n"/>
-      <c r="C141" s="9" t="n"/>
-      <c r="D141" s="10" t="n"/>
-      <c r="E141" s="11" t="n"/>
-      <c r="F141" s="9" t="n"/>
-      <c r="G141" s="9" t="n"/>
+      <c r="B141" s="9" t="n"/>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="11" t="n"/>
+      <c r="E141" s="12" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
     </row>
     <row r="142" ht="21" customHeight="1">
-      <c r="A142" s="7">
+      <c r="A142" s="8">
         <f>IF(B142="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B142" s="8" t="n"/>
-      <c r="C142" s="9" t="n"/>
-      <c r="D142" s="10" t="n"/>
-      <c r="E142" s="11" t="n"/>
-      <c r="F142" s="9" t="n"/>
-      <c r="G142" s="9" t="n"/>
+      <c r="B142" s="9" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="11" t="n"/>
+      <c r="E142" s="12" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
     </row>
     <row r="143" ht="21" customHeight="1">
-      <c r="A143" s="7">
+      <c r="A143" s="8">
         <f>IF(B143="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B143" s="8" t="n"/>
-      <c r="C143" s="9" t="n"/>
-      <c r="D143" s="10" t="n"/>
-      <c r="E143" s="11" t="n"/>
-      <c r="F143" s="9" t="n"/>
-      <c r="G143" s="9" t="n"/>
+      <c r="B143" s="9" t="n"/>
+      <c r="C143" s="10" t="n"/>
+      <c r="D143" s="11" t="n"/>
+      <c r="E143" s="12" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
     </row>
     <row r="144" ht="21" customHeight="1">
-      <c r="A144" s="7">
+      <c r="A144" s="8">
         <f>IF(B144="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B144" s="8" t="n"/>
-      <c r="C144" s="9" t="n"/>
-      <c r="D144" s="10" t="n"/>
-      <c r="E144" s="11" t="n"/>
-      <c r="F144" s="9" t="n"/>
-      <c r="G144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="11" t="n"/>
+      <c r="E144" s="12" t="n"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
     </row>
     <row r="145" ht="21" customHeight="1">
-      <c r="A145" s="7">
+      <c r="A145" s="8">
         <f>IF(B145="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="9" t="n"/>
-      <c r="D145" s="10" t="n"/>
-      <c r="E145" s="11" t="n"/>
-      <c r="F145" s="9" t="n"/>
-      <c r="G145" s="9" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="11" t="n"/>
+      <c r="E145" s="12" t="n"/>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
     </row>
     <row r="146" ht="21" customHeight="1">
-      <c r="A146" s="7">
+      <c r="A146" s="8">
         <f>IF(B146="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="9" t="n"/>
-      <c r="D146" s="10" t="n"/>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="9" t="n"/>
-      <c r="G146" s="9" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="11" t="n"/>
+      <c r="E146" s="12" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
     </row>
     <row r="147" ht="21" customHeight="1">
-      <c r="A147" s="7">
+      <c r="A147" s="8">
         <f>IF(B147="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B147" s="8" t="n"/>
-      <c r="C147" s="9" t="n"/>
-      <c r="D147" s="10" t="n"/>
-      <c r="E147" s="11" t="n"/>
-      <c r="F147" s="9" t="n"/>
-      <c r="G147" s="9" t="n"/>
+      <c r="B147" s="9" t="n"/>
+      <c r="C147" s="10" t="n"/>
+      <c r="D147" s="11" t="n"/>
+      <c r="E147" s="12" t="n"/>
+      <c r="F147" s="10" t="n"/>
+      <c r="G147" s="10" t="n"/>
     </row>
     <row r="148" ht="21" customHeight="1">
-      <c r="A148" s="7">
+      <c r="A148" s="8">
         <f>IF(B148="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B148" s="8" t="n"/>
-      <c r="C148" s="9" t="n"/>
-      <c r="D148" s="10" t="n"/>
-      <c r="E148" s="11" t="n"/>
-      <c r="F148" s="9" t="n"/>
-      <c r="G148" s="9" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="10" t="n"/>
+      <c r="D148" s="11" t="n"/>
+      <c r="E148" s="12" t="n"/>
+      <c r="F148" s="10" t="n"/>
+      <c r="G148" s="10" t="n"/>
     </row>
     <row r="149" ht="21" customHeight="1">
-      <c r="A149" s="7">
+      <c r="A149" s="8">
         <f>IF(B149="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B149" s="8" t="n"/>
-      <c r="C149" s="9" t="n"/>
-      <c r="D149" s="10" t="n"/>
-      <c r="E149" s="11" t="n"/>
-      <c r="F149" s="9" t="n"/>
-      <c r="G149" s="9" t="n"/>
+      <c r="B149" s="9" t="n"/>
+      <c r="C149" s="10" t="n"/>
+      <c r="D149" s="11" t="n"/>
+      <c r="E149" s="12" t="n"/>
+      <c r="F149" s="10" t="n"/>
+      <c r="G149" s="10" t="n"/>
     </row>
     <row r="150" ht="21" customHeight="1">
-      <c r="A150" s="7">
+      <c r="A150" s="8">
         <f>IF(B150="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B150" s="8" t="n"/>
-      <c r="C150" s="9" t="n"/>
-      <c r="D150" s="10" t="n"/>
-      <c r="E150" s="11" t="n"/>
-      <c r="F150" s="9" t="n"/>
-      <c r="G150" s="9" t="n"/>
+      <c r="B150" s="9" t="n"/>
+      <c r="C150" s="10" t="n"/>
+      <c r="D150" s="11" t="n"/>
+      <c r="E150" s="12" t="n"/>
+      <c r="F150" s="10" t="n"/>
+      <c r="G150" s="10" t="n"/>
     </row>
     <row r="151" ht="21" customHeight="1">
-      <c r="A151" s="7">
+      <c r="A151" s="8">
         <f>IF(B151="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B151" s="8" t="n"/>
-      <c r="C151" s="9" t="n"/>
-      <c r="D151" s="10" t="n"/>
-      <c r="E151" s="11" t="n"/>
-      <c r="F151" s="9" t="n"/>
-      <c r="G151" s="9" t="n"/>
+      <c r="B151" s="9" t="n"/>
+      <c r="C151" s="10" t="n"/>
+      <c r="D151" s="11" t="n"/>
+      <c r="E151" s="12" t="n"/>
+      <c r="F151" s="10" t="n"/>
+      <c r="G151" s="10" t="n"/>
     </row>
     <row r="152" ht="21" customHeight="1">
-      <c r="A152" s="7">
+      <c r="A152" s="8">
         <f>IF(B152="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B152" s="8" t="n"/>
-      <c r="C152" s="9" t="n"/>
-      <c r="D152" s="10" t="n"/>
-      <c r="E152" s="11" t="n"/>
-      <c r="F152" s="9" t="n"/>
-      <c r="G152" s="9" t="n"/>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="10" t="n"/>
+      <c r="D152" s="11" t="n"/>
+      <c r="E152" s="12" t="n"/>
+      <c r="F152" s="10" t="n"/>
+      <c r="G152" s="10" t="n"/>
     </row>
     <row r="153" ht="21" customHeight="1">
-      <c r="A153" s="7">
+      <c r="A153" s="8">
         <f>IF(B153="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B153" s="8" t="n"/>
-      <c r="C153" s="9" t="n"/>
-      <c r="D153" s="10" t="n"/>
-      <c r="E153" s="11" t="n"/>
-      <c r="F153" s="9" t="n"/>
-      <c r="G153" s="9" t="n"/>
+      <c r="B153" s="9" t="n"/>
+      <c r="C153" s="10" t="n"/>
+      <c r="D153" s="11" t="n"/>
+      <c r="E153" s="12" t="n"/>
+      <c r="F153" s="10" t="n"/>
+      <c r="G153" s="10" t="n"/>
     </row>
     <row r="154" ht="21" customHeight="1">
-      <c r="A154" s="7">
+      <c r="A154" s="8">
         <f>IF(B154="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B154" s="8" t="n"/>
-      <c r="C154" s="9" t="n"/>
-      <c r="D154" s="10" t="n"/>
-      <c r="E154" s="11" t="n"/>
-      <c r="F154" s="9" t="n"/>
-      <c r="G154" s="9" t="n"/>
+      <c r="B154" s="9" t="n"/>
+      <c r="C154" s="10" t="n"/>
+      <c r="D154" s="11" t="n"/>
+      <c r="E154" s="12" t="n"/>
+      <c r="F154" s="10" t="n"/>
+      <c r="G154" s="10" t="n"/>
     </row>
     <row r="155" ht="21" customHeight="1">
-      <c r="A155" s="7">
+      <c r="A155" s="8">
         <f>IF(B155="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B155" s="8" t="n"/>
-      <c r="C155" s="9" t="n"/>
-      <c r="D155" s="10" t="n"/>
-      <c r="E155" s="11" t="n"/>
-      <c r="F155" s="9" t="n"/>
-      <c r="G155" s="9" t="n"/>
+      <c r="B155" s="9" t="n"/>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="11" t="n"/>
+      <c r="E155" s="12" t="n"/>
+      <c r="F155" s="10" t="n"/>
+      <c r="G155" s="10" t="n"/>
     </row>
     <row r="156" ht="21" customHeight="1">
-      <c r="A156" s="7">
+      <c r="A156" s="8">
         <f>IF(B156="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B156" s="8" t="n"/>
-      <c r="C156" s="9" t="n"/>
-      <c r="D156" s="10" t="n"/>
-      <c r="E156" s="11" t="n"/>
-      <c r="F156" s="9" t="n"/>
-      <c r="G156" s="9" t="n"/>
+      <c r="B156" s="9" t="n"/>
+      <c r="C156" s="10" t="n"/>
+      <c r="D156" s="11" t="n"/>
+      <c r="E156" s="12" t="n"/>
+      <c r="F156" s="10" t="n"/>
+      <c r="G156" s="10" t="n"/>
     </row>
     <row r="157" ht="21" customHeight="1">
-      <c r="A157" s="7">
+      <c r="A157" s="8">
         <f>IF(B157="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B157" s="8" t="n"/>
-      <c r="C157" s="9" t="n"/>
-      <c r="D157" s="10" t="n"/>
-      <c r="E157" s="11" t="n"/>
-      <c r="F157" s="9" t="n"/>
-      <c r="G157" s="9" t="n"/>
+      <c r="B157" s="9" t="n"/>
+      <c r="C157" s="10" t="n"/>
+      <c r="D157" s="11" t="n"/>
+      <c r="E157" s="12" t="n"/>
+      <c r="F157" s="10" t="n"/>
+      <c r="G157" s="10" t="n"/>
     </row>
     <row r="158" ht="21" customHeight="1">
-      <c r="A158" s="7">
+      <c r="A158" s="8">
         <f>IF(B158="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B158" s="8" t="n"/>
-      <c r="C158" s="9" t="n"/>
-      <c r="D158" s="10" t="n"/>
-      <c r="E158" s="11" t="n"/>
-      <c r="F158" s="9" t="n"/>
-      <c r="G158" s="9" t="n"/>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="10" t="n"/>
+      <c r="D158" s="11" t="n"/>
+      <c r="E158" s="12" t="n"/>
+      <c r="F158" s="10" t="n"/>
+      <c r="G158" s="10" t="n"/>
     </row>
     <row r="159" ht="21" customHeight="1">
-      <c r="A159" s="7">
+      <c r="A159" s="8">
         <f>IF(B159="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B159" s="8" t="n"/>
-      <c r="C159" s="9" t="n"/>
-      <c r="D159" s="10" t="n"/>
-      <c r="E159" s="11" t="n"/>
-      <c r="F159" s="9" t="n"/>
-      <c r="G159" s="9" t="n"/>
+      <c r="B159" s="9" t="n"/>
+      <c r="C159" s="10" t="n"/>
+      <c r="D159" s="11" t="n"/>
+      <c r="E159" s="12" t="n"/>
+      <c r="F159" s="10" t="n"/>
+      <c r="G159" s="10" t="n"/>
     </row>
     <row r="160" ht="21" customHeight="1">
-      <c r="A160" s="7">
+      <c r="A160" s="8">
         <f>IF(B160="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="9" t="n"/>
-      <c r="D160" s="10" t="n"/>
-      <c r="E160" s="11" t="n"/>
-      <c r="F160" s="9" t="n"/>
-      <c r="G160" s="9" t="n"/>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="10" t="n"/>
+      <c r="D160" s="11" t="n"/>
+      <c r="E160" s="12" t="n"/>
+      <c r="F160" s="10" t="n"/>
+      <c r="G160" s="10" t="n"/>
     </row>
     <row r="161" ht="21" customHeight="1">
-      <c r="A161" s="7">
+      <c r="A161" s="8">
         <f>IF(B161="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B161" s="8" t="n"/>
-      <c r="C161" s="9" t="n"/>
-      <c r="D161" s="10" t="n"/>
-      <c r="E161" s="11" t="n"/>
-      <c r="F161" s="9" t="n"/>
-      <c r="G161" s="9" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="10" t="n"/>
+      <c r="D161" s="11" t="n"/>
+      <c r="E161" s="12" t="n"/>
+      <c r="F161" s="10" t="n"/>
+      <c r="G161" s="10" t="n"/>
     </row>
     <row r="162" ht="21" customHeight="1">
-      <c r="A162" s="7">
+      <c r="A162" s="8">
         <f>IF(B162="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B162" s="8" t="n"/>
-      <c r="C162" s="9" t="n"/>
-      <c r="D162" s="10" t="n"/>
-      <c r="E162" s="11" t="n"/>
-      <c r="F162" s="9" t="n"/>
-      <c r="G162" s="9" t="n"/>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="10" t="n"/>
+      <c r="D162" s="11" t="n"/>
+      <c r="E162" s="12" t="n"/>
+      <c r="F162" s="10" t="n"/>
+      <c r="G162" s="10" t="n"/>
     </row>
     <row r="163" ht="21" customHeight="1">
-      <c r="A163" s="7">
+      <c r="A163" s="8">
         <f>IF(B163="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B163" s="8" t="n"/>
-      <c r="C163" s="9" t="n"/>
-      <c r="D163" s="10" t="n"/>
-      <c r="E163" s="11" t="n"/>
-      <c r="F163" s="9" t="n"/>
-      <c r="G163" s="9" t="n"/>
+      <c r="B163" s="9" t="n"/>
+      <c r="C163" s="10" t="n"/>
+      <c r="D163" s="11" t="n"/>
+      <c r="E163" s="12" t="n"/>
+      <c r="F163" s="10" t="n"/>
+      <c r="G163" s="10" t="n"/>
     </row>
     <row r="164" ht="21" customHeight="1">
-      <c r="A164" s="7">
+      <c r="A164" s="8">
         <f>IF(B164="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="9" t="n"/>
-      <c r="D164" s="10" t="n"/>
-      <c r="E164" s="11" t="n"/>
-      <c r="F164" s="9" t="n"/>
-      <c r="G164" s="9" t="n"/>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="10" t="n"/>
+      <c r="D164" s="11" t="n"/>
+      <c r="E164" s="12" t="n"/>
+      <c r="F164" s="10" t="n"/>
+      <c r="G164" s="10" t="n"/>
     </row>
     <row r="165" ht="21" customHeight="1">
-      <c r="A165" s="7">
+      <c r="A165" s="8">
         <f>IF(B165="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B165" s="8" t="n"/>
-      <c r="C165" s="9" t="n"/>
-      <c r="D165" s="10" t="n"/>
-      <c r="E165" s="11" t="n"/>
-      <c r="F165" s="9" t="n"/>
-      <c r="G165" s="9" t="n"/>
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="10" t="n"/>
+      <c r="D165" s="11" t="n"/>
+      <c r="E165" s="12" t="n"/>
+      <c r="F165" s="10" t="n"/>
+      <c r="G165" s="10" t="n"/>
     </row>
     <row r="166" ht="21" customHeight="1">
-      <c r="A166" s="7">
+      <c r="A166" s="8">
         <f>IF(B166="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B166" s="8" t="n"/>
-      <c r="C166" s="9" t="n"/>
-      <c r="D166" s="10" t="n"/>
-      <c r="E166" s="11" t="n"/>
-      <c r="F166" s="9" t="n"/>
-      <c r="G166" s="9" t="n"/>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="10" t="n"/>
+      <c r="D166" s="11" t="n"/>
+      <c r="E166" s="12" t="n"/>
+      <c r="F166" s="10" t="n"/>
+      <c r="G166" s="10" t="n"/>
     </row>
     <row r="167" ht="21" customHeight="1">
-      <c r="A167" s="7">
+      <c r="A167" s="8">
         <f>IF(B167="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B167" s="8" t="n"/>
-      <c r="C167" s="9" t="n"/>
-      <c r="D167" s="10" t="n"/>
-      <c r="E167" s="11" t="n"/>
-      <c r="F167" s="9" t="n"/>
-      <c r="G167" s="9" t="n"/>
+      <c r="B167" s="9" t="n"/>
+      <c r="C167" s="10" t="n"/>
+      <c r="D167" s="11" t="n"/>
+      <c r="E167" s="12" t="n"/>
+      <c r="F167" s="10" t="n"/>
+      <c r="G167" s="10" t="n"/>
     </row>
     <row r="168" ht="21" customHeight="1">
-      <c r="A168" s="7">
+      <c r="A168" s="8">
         <f>IF(B168="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B168" s="8" t="n"/>
-      <c r="C168" s="9" t="n"/>
-      <c r="D168" s="10" t="n"/>
-      <c r="E168" s="11" t="n"/>
-      <c r="F168" s="9" t="n"/>
-      <c r="G168" s="9" t="n"/>
+      <c r="B168" s="9" t="n"/>
+      <c r="C168" s="10" t="n"/>
+      <c r="D168" s="11" t="n"/>
+      <c r="E168" s="12" t="n"/>
+      <c r="F168" s="10" t="n"/>
+      <c r="G168" s="10" t="n"/>
     </row>
     <row r="169" ht="21" customHeight="1">
-      <c r="A169" s="7">
+      <c r="A169" s="8">
         <f>IF(B169="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B169" s="8" t="n"/>
-      <c r="C169" s="9" t="n"/>
-      <c r="D169" s="10" t="n"/>
-      <c r="E169" s="11" t="n"/>
-      <c r="F169" s="9" t="n"/>
-      <c r="G169" s="9" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="10" t="n"/>
+      <c r="D169" s="11" t="n"/>
+      <c r="E169" s="12" t="n"/>
+      <c r="F169" s="10" t="n"/>
+      <c r="G169" s="10" t="n"/>
     </row>
     <row r="170" ht="21" customHeight="1">
-      <c r="A170" s="7">
+      <c r="A170" s="8">
         <f>IF(B170="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B170" s="8" t="n"/>
-      <c r="C170" s="9" t="n"/>
-      <c r="D170" s="10" t="n"/>
-      <c r="E170" s="11" t="n"/>
-      <c r="F170" s="9" t="n"/>
-      <c r="G170" s="9" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="10" t="n"/>
+      <c r="D170" s="11" t="n"/>
+      <c r="E170" s="12" t="n"/>
+      <c r="F170" s="10" t="n"/>
+      <c r="G170" s="10" t="n"/>
     </row>
     <row r="171" ht="21" customHeight="1">
-      <c r="A171" s="7">
+      <c r="A171" s="8">
         <f>IF(B171="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="9" t="n"/>
-      <c r="D171" s="10" t="n"/>
-      <c r="E171" s="11" t="n"/>
-      <c r="F171" s="9" t="n"/>
-      <c r="G171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="10" t="n"/>
+      <c r="D171" s="11" t="n"/>
+      <c r="E171" s="12" t="n"/>
+      <c r="F171" s="10" t="n"/>
+      <c r="G171" s="10" t="n"/>
     </row>
     <row r="172" ht="21" customHeight="1">
-      <c r="A172" s="7">
+      <c r="A172" s="8">
         <f>IF(B172="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B172" s="8" t="n"/>
-      <c r="C172" s="9" t="n"/>
-      <c r="D172" s="10" t="n"/>
-      <c r="E172" s="11" t="n"/>
-      <c r="F172" s="9" t="n"/>
-      <c r="G172" s="9" t="n"/>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="10" t="n"/>
+      <c r="D172" s="11" t="n"/>
+      <c r="E172" s="12" t="n"/>
+      <c r="F172" s="10" t="n"/>
+      <c r="G172" s="10" t="n"/>
     </row>
     <row r="173" ht="21" customHeight="1">
-      <c r="A173" s="7">
+      <c r="A173" s="8">
         <f>IF(B173="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B173" s="8" t="n"/>
-      <c r="C173" s="9" t="n"/>
-      <c r="D173" s="10" t="n"/>
-      <c r="E173" s="11" t="n"/>
-      <c r="F173" s="9" t="n"/>
-      <c r="G173" s="9" t="n"/>
+      <c r="B173" s="9" t="n"/>
+      <c r="C173" s="10" t="n"/>
+      <c r="D173" s="11" t="n"/>
+      <c r="E173" s="12" t="n"/>
+      <c r="F173" s="10" t="n"/>
+      <c r="G173" s="10" t="n"/>
     </row>
     <row r="174" ht="21" customHeight="1">
-      <c r="A174" s="7">
+      <c r="A174" s="8">
         <f>IF(B174="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B174" s="8" t="n"/>
-      <c r="C174" s="9" t="n"/>
-      <c r="D174" s="10" t="n"/>
-      <c r="E174" s="11" t="n"/>
-      <c r="F174" s="9" t="n"/>
-      <c r="G174" s="9" t="n"/>
+      <c r="B174" s="9" t="n"/>
+      <c r="C174" s="10" t="n"/>
+      <c r="D174" s="11" t="n"/>
+      <c r="E174" s="12" t="n"/>
+      <c r="F174" s="10" t="n"/>
+      <c r="G174" s="10" t="n"/>
     </row>
     <row r="175" ht="21" customHeight="1">
-      <c r="A175" s="7">
+      <c r="A175" s="8">
         <f>IF(B175="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B175" s="8" t="n"/>
-      <c r="C175" s="9" t="n"/>
-      <c r="D175" s="10" t="n"/>
-      <c r="E175" s="11" t="n"/>
-      <c r="F175" s="9" t="n"/>
-      <c r="G175" s="9" t="n"/>
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="10" t="n"/>
+      <c r="D175" s="11" t="n"/>
+      <c r="E175" s="12" t="n"/>
+      <c r="F175" s="10" t="n"/>
+      <c r="G175" s="10" t="n"/>
     </row>
     <row r="176" ht="21" customHeight="1">
-      <c r="A176" s="7">
+      <c r="A176" s="8">
         <f>IF(B176="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B176" s="8" t="n"/>
-      <c r="C176" s="9" t="n"/>
-      <c r="D176" s="10" t="n"/>
-      <c r="E176" s="11" t="n"/>
-      <c r="F176" s="9" t="n"/>
-      <c r="G176" s="9" t="n"/>
+      <c r="B176" s="9" t="n"/>
+      <c r="C176" s="10" t="n"/>
+      <c r="D176" s="11" t="n"/>
+      <c r="E176" s="12" t="n"/>
+      <c r="F176" s="10" t="n"/>
+      <c r="G176" s="10" t="n"/>
     </row>
     <row r="177" ht="21" customHeight="1">
-      <c r="A177" s="7">
+      <c r="A177" s="8">
         <f>IF(B177="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B177" s="8" t="n"/>
-      <c r="C177" s="9" t="n"/>
-      <c r="D177" s="10" t="n"/>
-      <c r="E177" s="11" t="n"/>
-      <c r="F177" s="9" t="n"/>
-      <c r="G177" s="9" t="n"/>
+      <c r="B177" s="9" t="n"/>
+      <c r="C177" s="10" t="n"/>
+      <c r="D177" s="11" t="n"/>
+      <c r="E177" s="12" t="n"/>
+      <c r="F177" s="10" t="n"/>
+      <c r="G177" s="10" t="n"/>
     </row>
     <row r="178" ht="21" customHeight="1">
-      <c r="A178" s="7">
+      <c r="A178" s="8">
         <f>IF(B178="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B178" s="8" t="n"/>
-      <c r="C178" s="9" t="n"/>
-      <c r="D178" s="10" t="n"/>
-      <c r="E178" s="11" t="n"/>
-      <c r="F178" s="9" t="n"/>
-      <c r="G178" s="9" t="n"/>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="10" t="n"/>
+      <c r="D178" s="11" t="n"/>
+      <c r="E178" s="12" t="n"/>
+      <c r="F178" s="10" t="n"/>
+      <c r="G178" s="10" t="n"/>
     </row>
     <row r="179" ht="21" customHeight="1">
-      <c r="A179" s="7">
+      <c r="A179" s="8">
         <f>IF(B179="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B179" s="8" t="n"/>
-      <c r="C179" s="9" t="n"/>
-      <c r="D179" s="10" t="n"/>
-      <c r="E179" s="11" t="n"/>
-      <c r="F179" s="9" t="n"/>
-      <c r="G179" s="9" t="n"/>
+      <c r="B179" s="9" t="n"/>
+      <c r="C179" s="10" t="n"/>
+      <c r="D179" s="11" t="n"/>
+      <c r="E179" s="12" t="n"/>
+      <c r="F179" s="10" t="n"/>
+      <c r="G179" s="10" t="n"/>
     </row>
     <row r="180" ht="21" customHeight="1">
-      <c r="A180" s="7">
+      <c r="A180" s="8">
         <f>IF(B180="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B180" s="8" t="n"/>
-      <c r="C180" s="9" t="n"/>
-      <c r="D180" s="10" t="n"/>
-      <c r="E180" s="11" t="n"/>
-      <c r="F180" s="9" t="n"/>
-      <c r="G180" s="9" t="n"/>
+      <c r="B180" s="9" t="n"/>
+      <c r="C180" s="10" t="n"/>
+      <c r="D180" s="11" t="n"/>
+      <c r="E180" s="12" t="n"/>
+      <c r="F180" s="10" t="n"/>
+      <c r="G180" s="10" t="n"/>
     </row>
     <row r="181" ht="21" customHeight="1">
-      <c r="A181" s="7">
+      <c r="A181" s="8">
         <f>IF(B181="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B181" s="8" t="n"/>
-      <c r="C181" s="9" t="n"/>
-      <c r="D181" s="10" t="n"/>
-      <c r="E181" s="11" t="n"/>
-      <c r="F181" s="9" t="n"/>
-      <c r="G181" s="9" t="n"/>
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="10" t="n"/>
+      <c r="D181" s="11" t="n"/>
+      <c r="E181" s="12" t="n"/>
+      <c r="F181" s="10" t="n"/>
+      <c r="G181" s="10" t="n"/>
     </row>
     <row r="182" ht="21" customHeight="1">
-      <c r="A182" s="7">
+      <c r="A182" s="8">
         <f>IF(B182="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B182" s="8" t="n"/>
-      <c r="C182" s="9" t="n"/>
-      <c r="D182" s="10" t="n"/>
-      <c r="E182" s="11" t="n"/>
-      <c r="F182" s="9" t="n"/>
-      <c r="G182" s="9" t="n"/>
+      <c r="B182" s="9" t="n"/>
+      <c r="C182" s="10" t="n"/>
+      <c r="D182" s="11" t="n"/>
+      <c r="E182" s="12" t="n"/>
+      <c r="F182" s="10" t="n"/>
+      <c r="G182" s="10" t="n"/>
     </row>
     <row r="183" ht="21" customHeight="1">
-      <c r="A183" s="7">
+      <c r="A183" s="8">
         <f>IF(B183="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B183" s="8" t="n"/>
-      <c r="C183" s="9" t="n"/>
-      <c r="D183" s="10" t="n"/>
-      <c r="E183" s="11" t="n"/>
-      <c r="F183" s="9" t="n"/>
-      <c r="G183" s="9" t="n"/>
+      <c r="B183" s="9" t="n"/>
+      <c r="C183" s="10" t="n"/>
+      <c r="D183" s="11" t="n"/>
+      <c r="E183" s="12" t="n"/>
+      <c r="F183" s="10" t="n"/>
+      <c r="G183" s="10" t="n"/>
     </row>
     <row r="184" ht="21" customHeight="1">
-      <c r="A184" s="7">
+      <c r="A184" s="8">
         <f>IF(B184="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="9" t="n"/>
-      <c r="D184" s="10" t="n"/>
-      <c r="E184" s="11" t="n"/>
-      <c r="F184" s="9" t="n"/>
-      <c r="G184" s="9" t="n"/>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="10" t="n"/>
+      <c r="D184" s="11" t="n"/>
+      <c r="E184" s="12" t="n"/>
+      <c r="F184" s="10" t="n"/>
+      <c r="G184" s="10" t="n"/>
     </row>
     <row r="185" ht="21" customHeight="1">
-      <c r="A185" s="7">
+      <c r="A185" s="8">
         <f>IF(B185="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="9" t="n"/>
-      <c r="D185" s="10" t="n"/>
-      <c r="E185" s="11" t="n"/>
-      <c r="F185" s="9" t="n"/>
-      <c r="G185" s="9" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="10" t="n"/>
+      <c r="D185" s="11" t="n"/>
+      <c r="E185" s="12" t="n"/>
+      <c r="F185" s="10" t="n"/>
+      <c r="G185" s="10" t="n"/>
     </row>
     <row r="186" ht="21" customHeight="1">
-      <c r="A186" s="7">
+      <c r="A186" s="8">
         <f>IF(B186="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B186" s="8" t="n"/>
-      <c r="C186" s="9" t="n"/>
-      <c r="D186" s="10" t="n"/>
-      <c r="E186" s="11" t="n"/>
-      <c r="F186" s="9" t="n"/>
-      <c r="G186" s="9" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="10" t="n"/>
+      <c r="D186" s="11" t="n"/>
+      <c r="E186" s="12" t="n"/>
+      <c r="F186" s="10" t="n"/>
+      <c r="G186" s="10" t="n"/>
     </row>
     <row r="187" ht="21" customHeight="1">
-      <c r="A187" s="7">
+      <c r="A187" s="8">
         <f>IF(B187="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="9" t="n"/>
-      <c r="D187" s="10" t="n"/>
-      <c r="E187" s="11" t="n"/>
-      <c r="F187" s="9" t="n"/>
-      <c r="G187" s="9" t="n"/>
+      <c r="B187" s="9" t="n"/>
+      <c r="C187" s="10" t="n"/>
+      <c r="D187" s="11" t="n"/>
+      <c r="E187" s="12" t="n"/>
+      <c r="F187" s="10" t="n"/>
+      <c r="G187" s="10" t="n"/>
     </row>
     <row r="188" ht="21" customHeight="1">
-      <c r="A188" s="7">
+      <c r="A188" s="8">
         <f>IF(B188="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B188" s="8" t="n"/>
-      <c r="C188" s="9" t="n"/>
-      <c r="D188" s="10" t="n"/>
-      <c r="E188" s="11" t="n"/>
-      <c r="F188" s="9" t="n"/>
-      <c r="G188" s="9" t="n"/>
+      <c r="B188" s="9" t="n"/>
+      <c r="C188" s="10" t="n"/>
+      <c r="D188" s="11" t="n"/>
+      <c r="E188" s="12" t="n"/>
+      <c r="F188" s="10" t="n"/>
+      <c r="G188" s="10" t="n"/>
     </row>
     <row r="189" ht="21" customHeight="1">
-      <c r="A189" s="7">
+      <c r="A189" s="8">
         <f>IF(B189="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="9" t="n"/>
-      <c r="D189" s="10" t="n"/>
-      <c r="E189" s="11" t="n"/>
-      <c r="F189" s="9" t="n"/>
-      <c r="G189" s="9" t="n"/>
+      <c r="B189" s="9" t="n"/>
+      <c r="C189" s="10" t="n"/>
+      <c r="D189" s="11" t="n"/>
+      <c r="E189" s="12" t="n"/>
+      <c r="F189" s="10" t="n"/>
+      <c r="G189" s="10" t="n"/>
     </row>
     <row r="190" ht="21" customHeight="1">
-      <c r="A190" s="7">
+      <c r="A190" s="8">
         <f>IF(B190="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B190" s="8" t="n"/>
-      <c r="C190" s="9" t="n"/>
-      <c r="D190" s="10" t="n"/>
-      <c r="E190" s="11" t="n"/>
-      <c r="F190" s="9" t="n"/>
-      <c r="G190" s="9" t="n"/>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="10" t="n"/>
+      <c r="D190" s="11" t="n"/>
+      <c r="E190" s="12" t="n"/>
+      <c r="F190" s="10" t="n"/>
+      <c r="G190" s="10" t="n"/>
     </row>
     <row r="191" ht="21" customHeight="1">
-      <c r="A191" s="7">
+      <c r="A191" s="8">
         <f>IF(B191="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B191" s="8" t="n"/>
-      <c r="C191" s="9" t="n"/>
-      <c r="D191" s="10" t="n"/>
-      <c r="E191" s="11" t="n"/>
-      <c r="F191" s="9" t="n"/>
-      <c r="G191" s="9" t="n"/>
+      <c r="B191" s="9" t="n"/>
+      <c r="C191" s="10" t="n"/>
+      <c r="D191" s="11" t="n"/>
+      <c r="E191" s="12" t="n"/>
+      <c r="F191" s="10" t="n"/>
+      <c r="G191" s="10" t="n"/>
     </row>
     <row r="192" ht="21" customHeight="1">
-      <c r="A192" s="7">
+      <c r="A192" s="8">
         <f>IF(B192="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B192" s="8" t="n"/>
-      <c r="C192" s="9" t="n"/>
-      <c r="D192" s="10" t="n"/>
-      <c r="E192" s="11" t="n"/>
-      <c r="F192" s="9" t="n"/>
-      <c r="G192" s="9" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="10" t="n"/>
+      <c r="D192" s="11" t="n"/>
+      <c r="E192" s="12" t="n"/>
+      <c r="F192" s="10" t="n"/>
+      <c r="G192" s="10" t="n"/>
     </row>
     <row r="193" ht="21" customHeight="1">
-      <c r="A193" s="7">
+      <c r="A193" s="8">
         <f>IF(B193="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B193" s="8" t="n"/>
-      <c r="C193" s="9" t="n"/>
-      <c r="D193" s="10" t="n"/>
-      <c r="E193" s="11" t="n"/>
-      <c r="F193" s="9" t="n"/>
-      <c r="G193" s="9" t="n"/>
+      <c r="B193" s="9" t="n"/>
+      <c r="C193" s="10" t="n"/>
+      <c r="D193" s="11" t="n"/>
+      <c r="E193" s="12" t="n"/>
+      <c r="F193" s="10" t="n"/>
+      <c r="G193" s="10" t="n"/>
     </row>
     <row r="194" ht="21" customHeight="1">
-      <c r="A194" s="7">
+      <c r="A194" s="8">
         <f>IF(B194="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B194" s="8" t="n"/>
-      <c r="C194" s="9" t="n"/>
-      <c r="D194" s="10" t="n"/>
-      <c r="E194" s="11" t="n"/>
-      <c r="F194" s="9" t="n"/>
-      <c r="G194" s="9" t="n"/>
+      <c r="B194" s="9" t="n"/>
+      <c r="C194" s="10" t="n"/>
+      <c r="D194" s="11" t="n"/>
+      <c r="E194" s="12" t="n"/>
+      <c r="F194" s="10" t="n"/>
+      <c r="G194" s="10" t="n"/>
     </row>
     <row r="195" ht="21" customHeight="1">
-      <c r="A195" s="7">
+      <c r="A195" s="8">
         <f>IF(B195="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B195" s="8" t="n"/>
-      <c r="C195" s="9" t="n"/>
-      <c r="D195" s="10" t="n"/>
-      <c r="E195" s="11" t="n"/>
-      <c r="F195" s="9" t="n"/>
-      <c r="G195" s="9" t="n"/>
+      <c r="B195" s="9" t="n"/>
+      <c r="C195" s="10" t="n"/>
+      <c r="D195" s="11" t="n"/>
+      <c r="E195" s="12" t="n"/>
+      <c r="F195" s="10" t="n"/>
+      <c r="G195" s="10" t="n"/>
     </row>
     <row r="196" ht="21" customHeight="1">
-      <c r="A196" s="7">
+      <c r="A196" s="8">
         <f>IF(B196="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B196" s="8" t="n"/>
-      <c r="C196" s="9" t="n"/>
-      <c r="D196" s="10" t="n"/>
-      <c r="E196" s="11" t="n"/>
-      <c r="F196" s="9" t="n"/>
-      <c r="G196" s="9" t="n"/>
+      <c r="B196" s="9" t="n"/>
+      <c r="C196" s="10" t="n"/>
+      <c r="D196" s="11" t="n"/>
+      <c r="E196" s="12" t="n"/>
+      <c r="F196" s="10" t="n"/>
+      <c r="G196" s="10" t="n"/>
     </row>
     <row r="197" ht="21" customHeight="1">
-      <c r="A197" s="7">
+      <c r="A197" s="8">
         <f>IF(B197="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B197" s="8" t="n"/>
-      <c r="C197" s="9" t="n"/>
-      <c r="D197" s="10" t="n"/>
-      <c r="E197" s="11" t="n"/>
-      <c r="F197" s="9" t="n"/>
-      <c r="G197" s="9" t="n"/>
+      <c r="B197" s="9" t="n"/>
+      <c r="C197" s="10" t="n"/>
+      <c r="D197" s="11" t="n"/>
+      <c r="E197" s="12" t="n"/>
+      <c r="F197" s="10" t="n"/>
+      <c r="G197" s="10" t="n"/>
     </row>
     <row r="198" ht="21" customHeight="1">
-      <c r="A198" s="7">
+      <c r="A198" s="8">
         <f>IF(B198="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B198" s="8" t="n"/>
-      <c r="C198" s="9" t="n"/>
-      <c r="D198" s="10" t="n"/>
-      <c r="E198" s="11" t="n"/>
-      <c r="F198" s="9" t="n"/>
-      <c r="G198" s="9" t="n"/>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="10" t="n"/>
+      <c r="D198" s="11" t="n"/>
+      <c r="E198" s="12" t="n"/>
+      <c r="F198" s="10" t="n"/>
+      <c r="G198" s="10" t="n"/>
     </row>
     <row r="199" ht="21" customHeight="1">
-      <c r="A199" s="7">
+      <c r="A199" s="8">
         <f>IF(B199="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B199" s="8" t="n"/>
-      <c r="C199" s="9" t="n"/>
-      <c r="D199" s="10" t="n"/>
-      <c r="E199" s="11" t="n"/>
-      <c r="F199" s="9" t="n"/>
-      <c r="G199" s="9" t="n"/>
+      <c r="B199" s="9" t="n"/>
+      <c r="C199" s="10" t="n"/>
+      <c r="D199" s="11" t="n"/>
+      <c r="E199" s="12" t="n"/>
+      <c r="F199" s="10" t="n"/>
+      <c r="G199" s="10" t="n"/>
     </row>
     <row r="200" ht="21" customHeight="1">
-      <c r="A200" s="7">
+      <c r="A200" s="8">
         <f>IF(B200="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B200" s="8" t="n"/>
-      <c r="C200" s="9" t="n"/>
-      <c r="D200" s="10" t="n"/>
-      <c r="E200" s="11" t="n"/>
-      <c r="F200" s="9" t="n"/>
-      <c r="G200" s="9" t="n"/>
+      <c r="B200" s="9" t="n"/>
+      <c r="C200" s="10" t="n"/>
+      <c r="D200" s="11" t="n"/>
+      <c r="E200" s="12" t="n"/>
+      <c r="F200" s="10" t="n"/>
+      <c r="G200" s="10" t="n"/>
     </row>
     <row r="201" ht="21" customHeight="1">
-      <c r="A201" s="7">
+      <c r="A201" s="8">
         <f>IF(B201="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B201" s="8" t="n"/>
-      <c r="C201" s="9" t="n"/>
-      <c r="D201" s="10" t="n"/>
-      <c r="E201" s="11" t="n"/>
-      <c r="F201" s="9" t="n"/>
-      <c r="G201" s="9" t="n"/>
+      <c r="B201" s="9" t="n"/>
+      <c r="C201" s="10" t="n"/>
+      <c r="D201" s="11" t="n"/>
+      <c r="E201" s="12" t="n"/>
+      <c r="F201" s="10" t="n"/>
+      <c r="G201" s="10" t="n"/>
     </row>
     <row r="202" ht="21" customHeight="1">
-      <c r="A202" s="7">
+      <c r="A202" s="8">
         <f>IF(B202="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B202" s="8" t="n"/>
-      <c r="C202" s="9" t="n"/>
-      <c r="D202" s="10" t="n"/>
-      <c r="E202" s="11" t="n"/>
-      <c r="F202" s="9" t="n"/>
-      <c r="G202" s="9" t="n"/>
+      <c r="B202" s="9" t="n"/>
+      <c r="C202" s="10" t="n"/>
+      <c r="D202" s="11" t="n"/>
+      <c r="E202" s="12" t="n"/>
+      <c r="F202" s="10" t="n"/>
+      <c r="G202" s="10" t="n"/>
     </row>
     <row r="203" ht="21" customHeight="1">
-      <c r="A203" s="7">
+      <c r="A203" s="8">
         <f>IF(B203="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B203" s="8" t="n"/>
-      <c r="C203" s="9" t="n"/>
-      <c r="D203" s="10" t="n"/>
-      <c r="E203" s="11" t="n"/>
-      <c r="F203" s="9" t="n"/>
-      <c r="G203" s="9" t="n"/>
+      <c r="B203" s="9" t="n"/>
+      <c r="C203" s="10" t="n"/>
+      <c r="D203" s="11" t="n"/>
+      <c r="E203" s="12" t="n"/>
+      <c r="F203" s="10" t="n"/>
+      <c r="G203" s="10" t="n"/>
     </row>
     <row r="204" ht="21" customHeight="1">
-      <c r="A204" s="7">
+      <c r="A204" s="8">
         <f>IF(B204="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B204" s="8" t="n"/>
-      <c r="C204" s="9" t="n"/>
-      <c r="D204" s="10" t="n"/>
-      <c r="E204" s="11" t="n"/>
-      <c r="F204" s="9" t="n"/>
-      <c r="G204" s="9" t="n"/>
+      <c r="B204" s="9" t="n"/>
+      <c r="C204" s="10" t="n"/>
+      <c r="D204" s="11" t="n"/>
+      <c r="E204" s="12" t="n"/>
+      <c r="F204" s="10" t="n"/>
+      <c r="G204" s="10" t="n"/>
     </row>
     <row r="205" ht="21" customHeight="1">
-      <c r="A205" s="7">
+      <c r="A205" s="8">
         <f>IF(B205="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B205" s="8" t="n"/>
-      <c r="C205" s="9" t="n"/>
-      <c r="D205" s="10" t="n"/>
-      <c r="E205" s="11" t="n"/>
-      <c r="F205" s="9" t="n"/>
-      <c r="G205" s="9" t="n"/>
+      <c r="B205" s="9" t="n"/>
+      <c r="C205" s="10" t="n"/>
+      <c r="D205" s="11" t="n"/>
+      <c r="E205" s="12" t="n"/>
+      <c r="F205" s="10" t="n"/>
+      <c r="G205" s="10" t="n"/>
     </row>
     <row r="206" ht="21" customHeight="1">
-      <c r="A206" s="7">
+      <c r="A206" s="8">
         <f>IF(B206="","",ROW()-6)</f>
         <v/>
       </c>
-      <c r="B206" s="8" t="n"/>
-      <c r="C206" s="9" t="n"/>
-      <c r="D206" s="10" t="n"/>
-      <c r="E206" s="11" t="n"/>
-      <c r="F206" s="9" t="n"/>
-      <c r="G206" s="9" t="n"/>
+      <c r="B206" s="9" t="n"/>
+      <c r="C206" s="10" t="n"/>
+      <c r="D206" s="11" t="n"/>
+      <c r="E206" s="12" t="n"/>
+      <c r="F206" s="10" t="n"/>
+      <c r="G206" s="10" t="n"/>
     </row>
     <row r="207"/>
     <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="12" t="inlineStr">
+      <c r="A208" s="13" t="inlineStr">
         <is>
           <t>لا يُرسَل الملف إلا وكل بند مكتوب عليه اسم مدقِّقه</t>
         </is>
@@ -3171,9 +3184,6 @@
     <cfRule type="expression" priority="5" dxfId="3">
       <formula>$G7&lt;&gt;""</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="4">
-      <formula>AND(ISNUMBER($C7),$C7&lt;0)</formula>
-    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="G7:G206" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -3191,7 +3201,875 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>مرتجعات الورشة — محلات العون لمواد البناء</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>الورشة</t>
+        </is>
+      </c>
+      <c r="B2" s="15">
+        <f>IF('الورشة'!B2="","",'الورشة'!B2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>البنود المرتجعة</t>
+        </is>
+      </c>
+      <c r="B4" s="5">
+        <f>COUNTA(B7:B66)</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>المدقَّقة</t>
+        </is>
+      </c>
+      <c r="D4" s="5">
+        <f>COUNTA(G7:G66)</f>
+        <v/>
+      </c>
+      <c r="E4" s="6">
+        <f>IF(B4=0,"⛔ ما في بنود مُدخلة",IF(D4&lt;B4,"⛔ باقي "&amp;(B4-D4)&amp;" بند بدون تدقيق","✅ كل البنود مدقَّقة"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>الكمية</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>الإفرادي</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>المُرجِع</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>المدقق</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21" customHeight="1">
+      <c r="A7" s="8">
+        <f>IF(B7="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="8">
+        <f>IF(B8="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="21" customHeight="1">
+      <c r="A9" s="8">
+        <f>IF(B9="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="21" customHeight="1">
+      <c r="A10" s="8">
+        <f>IF(B10="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="A11" s="8">
+        <f>IF(B11="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="8">
+        <f>IF(B12="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="8">
+        <f>IF(B13="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="8">
+        <f>IF(B14="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="8">
+        <f>IF(B15="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="8">
+        <f>IF(B16="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="8">
+        <f>IF(B17="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="8">
+        <f>IF(B18="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="8">
+        <f>IF(B19="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="8">
+        <f>IF(B20="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="8">
+        <f>IF(B21="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="8">
+        <f>IF(B22="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="8">
+        <f>IF(B23="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="8">
+        <f>IF(B24="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="8">
+        <f>IF(B25="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" s="8">
+        <f>IF(B26="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="21" customHeight="1">
+      <c r="A27" s="8">
+        <f>IF(B27="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="21" customHeight="1">
+      <c r="A28" s="8">
+        <f>IF(B28="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="21" customHeight="1">
+      <c r="A29" s="8">
+        <f>IF(B29="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="8">
+        <f>IF(B30="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="8">
+        <f>IF(B31="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="8">
+        <f>IF(B32="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" s="8">
+        <f>IF(B33="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="21" customHeight="1">
+      <c r="A34" s="8">
+        <f>IF(B34="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1">
+      <c r="A35" s="8">
+        <f>IF(B35="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="21" customHeight="1">
+      <c r="A36" s="8">
+        <f>IF(B36="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="21" customHeight="1">
+      <c r="A37" s="8">
+        <f>IF(B37="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" s="8">
+        <f>IF(B38="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="8">
+        <f>IF(B39="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="21" customHeight="1">
+      <c r="A40" s="8">
+        <f>IF(B40="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="21" customHeight="1">
+      <c r="A41" s="8">
+        <f>IF(B41="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1">
+      <c r="A42" s="8">
+        <f>IF(B42="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+    </row>
+    <row r="43" ht="21" customHeight="1">
+      <c r="A43" s="8">
+        <f>IF(B43="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+    </row>
+    <row r="44" ht="21" customHeight="1">
+      <c r="A44" s="8">
+        <f>IF(B44="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+    </row>
+    <row r="45" ht="21" customHeight="1">
+      <c r="A45" s="8">
+        <f>IF(B45="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="8">
+        <f>IF(B46="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+    </row>
+    <row r="47" ht="21" customHeight="1">
+      <c r="A47" s="8">
+        <f>IF(B47="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+    </row>
+    <row r="48" ht="21" customHeight="1">
+      <c r="A48" s="8">
+        <f>IF(B48="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" s="8">
+        <f>IF(B49="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="8">
+        <f>IF(B50="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="11" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+    </row>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="8">
+        <f>IF(B51="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+    </row>
+    <row r="52" ht="21" customHeight="1">
+      <c r="A52" s="8">
+        <f>IF(B52="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1">
+      <c r="A53" s="8">
+        <f>IF(B53="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="11" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+    </row>
+    <row r="54" ht="21" customHeight="1">
+      <c r="A54" s="8">
+        <f>IF(B54="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+    </row>
+    <row r="55" ht="21" customHeight="1">
+      <c r="A55" s="8">
+        <f>IF(B55="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="11" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="21" customHeight="1">
+      <c r="A56" s="8">
+        <f>IF(B56="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="11" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+    </row>
+    <row r="57" ht="21" customHeight="1">
+      <c r="A57" s="8">
+        <f>IF(B57="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" s="8">
+        <f>IF(B58="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="11" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="21" customHeight="1">
+      <c r="A59" s="8">
+        <f>IF(B59="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="8">
+        <f>IF(B60="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="8">
+        <f>IF(B61="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="21" customHeight="1">
+      <c r="A62" s="8">
+        <f>IF(B62="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="8">
+        <f>IF(B63="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="21" customHeight="1">
+      <c r="A64" s="8">
+        <f>IF(B64="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="8">
+        <f>IF(B65="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+    </row>
+    <row r="66" ht="21" customHeight="1">
+      <c r="A66" s="8">
+        <f>IF(B66="","",ROW()-6)</f>
+        <v/>
+      </c>
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+    </row>
+    <row r="67"/>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>الإفرادي هنا = السعر اللي انباع فيه للمشروع، مش سعر الكتالوج</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
+  <mergeCells count="4">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT(E4,1)="✅"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>LEFT(E4,1)="⛔"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:C66">
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>AND($B7&lt;&gt;"",$C7="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:E66">
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>AND($B7&lt;&gt;"",$E7="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:G66">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>$G7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G7:G66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"عمر المصري,ابو علي"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3206,196 +4084,220 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>الموظف اللي بطلّع البضاعة</t>
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>ورقة «الورشة» — البضاعة اللي بتطلع</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>ورقة وحدة لكل ورشة، من أول بند لآخر بند. اسم الورشة بيتكتب مرة وحدة فوق وبس.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>أدخل البنود بند بند. وكل بند بتدخله — اشطبه بالقلم على الورقة الأصلية. أي بند بضل بدون شطب = بند نسيته. هاي أهم خطوة بكل النموذج.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>التاريخ إلزامي لكل بند — كل تاريخ بصير فاتورة لحاله بالنظام.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>الإفرادي: إذا المهندس اتفق مع المقاول على سعر، اكتبه. وإلا اتركه فاضي.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>المستلم: اكتب اسم اللي استلم البضاعة على كل بند.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>المرتجع</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>ورقة «المرتجعات» — البضاعة اللي بترجع</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>البضاعة الراجعة تنكتب سطر عادي بنفس الورقة، بتاريخ اليوم اللي رجعت فيه، والكمية بالسالب: «‎-5». السطر بيتلوّن برتقالي لحاله عشان ما ينقرأ غلط.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>المرتجعات لها ورقة مستقلة (التبويب البرتقالي). المرتجع ما بينكتب أبداً بورقة الورشة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>الإفرادي بسطر المرتجع = السعر اللي انباعت فيه، مش سعر الكتالوج. وإذا الراجع مكسور أو مفتوح وبدك تخصم عليه، اكتب سعر أقل — هاد اللي رح يترجع للمقاول.</t>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>اسم الورشة فوق بيتعبّى لحاله من ورقة الورشة — لا تكتبه.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>المستلم بسطر المرتجع = اللي رجّع البضاعة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>الكمية تنكتب عادي بالموجب — الورقة كلها مرتجعات، ما في داعي للسالب.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>الإفرادي = السعر اللي انباع فيه للمشروع، مش سعر الكتالوج. وإذا الراجع مكسور أو مفتوح وبدك تخصم، اكتب سعر أقل — هاد اللي رح يترجع للمقاول. وإذا ما بتعرف السعر اتركه فاضي وأنا بجيبه من فواتير المشروع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>المُرجِع: اسم اللي رجّع البضاعة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>المدقِّق — عمر المصري أو أبو علي</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>التدقيق من الورقة الأصلية، مش من الشاشة. امسك الورقة واقرأ منها.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «المدقق» لهذا البند.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق.</t>
-        </is>
-      </c>
-    </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>كل بند تتأكد منه (البند صح والعدد صح) — اختر اسمك بخانة «المدقق».</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>العدّاد فوق ما بيصير أخضر إلا لما كل بند مُدخل يكون عليه اسم مدقِّق. وكل ورقة إلها عدّادها — لازم الاثنين يصيروا أخضر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>ابعث الملف + صورة الورقة الأصلية للأستاذ.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>وقت الطباعة: حدّد المدى المعبّى فقط، لأنه الورقة فيها 200 سطر فاضي جاهزين للورشة كلها.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>وقت الطباعة: حدّد المدى المعبّى فقط، لأنه الورقة فيها سطور فاضية جاهزة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>الفكرة باختصار</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>البند المنسي ما بيترك أثر على الإكسل — عشان هيك التدقيق لازم يكون مقابل الورقة الأصلية لا مقابل الشاشة، ومعه شطب بالقلم على الورقة وقت الإدخال.</t>
         </is>
@@ -3403,8 +4305,8 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A3:B3"/>
